--- a/144/DQ Templates and Instructions/Topic 2 DQ 1/Topic 2 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 2 DQ 1/Topic 2 DQ 1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 2 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="8_{EC0CA368-B35E-4E61-BE63-B68E8477FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5232D9C-7D1B-464C-9057-BBC2BB43756E}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="8_{EC0CA368-B35E-4E61-BE63-B68E8477FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3808BB-37D4-41F7-8305-D783DD24AD34}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30DCFED0-AF9F-4763-8D9E-1F0E9BEB0013}"/>
+    <workbookView xWindow="0" yWindow="30" windowWidth="23010" windowHeight="12210" activeTab="1" xr2:uid="{30DCFED0-AF9F-4763-8D9E-1F0E9BEB0013}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="3" r:id="rId1"/>
@@ -584,7 +584,7 @@
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -682,12 +682,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1460,7 +1454,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="212">
+  <cellXfs count="209">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1737,8 +1731,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
@@ -1782,8 +1775,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="53" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
@@ -1798,8 +1790,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
@@ -1827,139 +1818,83 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" indent="1"/>
       <protection locked="0"/>
     </xf>
@@ -2049,60 +1984,181 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2129,59 +2185,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2208,18 +2211,6 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2718,63 +2709,63 @@
       <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="97" t="s">
+      <c r="D2" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="98"/>
-      <c r="F2" s="98"/>
-      <c r="G2" s="98"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="99"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="96"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="100"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="102"/>
+      <c r="D3" s="97"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="99"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="100"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="102"/>
+      <c r="D4" s="97"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="99"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="100"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="102"/>
+      <c r="D5" s="97"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="99"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="D6" s="100"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="102"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="99"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
-      <c r="F7" s="104"/>
-      <c r="G7" s="104"/>
-      <c r="H7" s="104"/>
-      <c r="I7" s="105"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="101"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="101"/>
+      <c r="I7" s="102"/>
     </row>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
       <c r="B8" s="52" t="s">
@@ -2803,7 +2794,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3C781E8-8BCA-4604-9AA0-98AEDF949CBB}">
-  <dimension ref="A1:T41"/>
+  <dimension ref="A1:S41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.42578125" customWidth="1"/>
@@ -2814,661 +2805,660 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="108"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="167"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="109"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
+      <c r="A2" s="168"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="109"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="111"/>
+      <c r="A3" s="168"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="169"/>
+      <c r="I3" s="169"/>
+      <c r="J3" s="169"/>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="169"/>
+      <c r="O3" s="169"/>
+      <c r="P3" s="170"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="109"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="111"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="170"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="109"/>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="111"/>
+      <c r="A5" s="168"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+      <c r="P5" s="170"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="109"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="111"/>
+      <c r="A6" s="168"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="170"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="109"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="111"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="170"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="109"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="110"/>
-      <c r="P8" s="111"/>
+      <c r="A8" s="168"/>
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="169"/>
+      <c r="E8" s="169"/>
+      <c r="F8" s="169"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="169"/>
+      <c r="I8" s="169"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+      <c r="P8" s="170"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="109"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="111"/>
+      <c r="A9" s="168"/>
+      <c r="B9" s="169"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
+      <c r="I9" s="169"/>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="169"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="169"/>
+      <c r="P9" s="170"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="109"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="111"/>
+      <c r="A10" s="168"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="169"/>
+      <c r="P10" s="170"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="113"/>
-      <c r="L11" s="113"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113"/>
-      <c r="O11" s="113"/>
-      <c r="P11" s="114"/>
+      <c r="A11" s="171"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="172"/>
+      <c r="H11" s="172"/>
+      <c r="I11" s="172"/>
+      <c r="J11" s="172"/>
+      <c r="K11" s="172"/>
+      <c r="L11" s="172"/>
+      <c r="M11" s="172"/>
+      <c r="N11" s="172"/>
+      <c r="O11" s="172"/>
+      <c r="P11" s="173"/>
     </row>
     <row r="12" spans="1:16" ht="30.75" thickBot="1">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="115"/>
+      <c r="D12" s="174"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="115" t="s">
+      <c r="G12" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="116"/>
+      <c r="H12" s="175"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="117"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>2.2046199999999998</v>
       </c>
-      <c r="G13" s="117" t="s">
+      <c r="G13" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="118"/>
-      <c r="J13" s="119" t="s">
+      <c r="H13" s="121"/>
+      <c r="J13" s="176" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="121"/>
+      <c r="K13" s="177"/>
+      <c r="L13" s="177"/>
+      <c r="M13" s="177"/>
+      <c r="N13" s="178"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="117"/>
+      <c r="D14" s="120"/>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
         <v>29.573499999999999</v>
       </c>
-      <c r="G14" s="117" t="s">
+      <c r="G14" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="118"/>
-      <c r="J14" s="122" t="s">
+      <c r="H14" s="121"/>
+      <c r="J14" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="123"/>
-      <c r="L14" s="122" t="s">
+      <c r="K14" s="149"/>
+      <c r="L14" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="117"/>
-      <c r="N14" s="118"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="121"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="117"/>
+      <c r="D15" s="120"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3">
         <v>28.349523125000001</v>
       </c>
-      <c r="G15" s="117" t="s">
+      <c r="G15" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="118"/>
-      <c r="J15" s="124" t="s">
+      <c r="H15" s="121"/>
+      <c r="J15" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="125"/>
-      <c r="L15" s="126" t="s">
+      <c r="K15" s="151"/>
+      <c r="L15" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="127"/>
-      <c r="N15" s="128"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="154"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="117"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2">
         <v>1000</v>
       </c>
-      <c r="G16" s="117" t="s">
+      <c r="G16" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="118"/>
-      <c r="J16" s="131" t="s">
+      <c r="H16" s="121"/>
+      <c r="J16" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="132"/>
-      <c r="L16" s="126" t="s">
+      <c r="K16" s="158"/>
+      <c r="L16" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="127"/>
-      <c r="N16" s="128"/>
-    </row>
-    <row r="17" spans="1:20">
+      <c r="M16" s="153"/>
+      <c r="N16" s="154"/>
+    </row>
+    <row r="17" spans="1:19">
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="117"/>
+      <c r="D17" s="120"/>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
         <v>1000</v>
       </c>
-      <c r="G17" s="117" t="s">
+      <c r="G17" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="118"/>
-      <c r="J17" s="133" t="s">
+      <c r="H17" s="121"/>
+      <c r="J17" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="134"/>
-      <c r="L17" s="126" t="s">
+      <c r="K17" s="160"/>
+      <c r="L17" s="152" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="127"/>
-      <c r="N17" s="128"/>
-    </row>
-    <row r="18" spans="1:20" ht="15.75" thickBot="1">
+      <c r="M17" s="153"/>
+      <c r="N17" s="154"/>
+    </row>
+    <row r="18" spans="1:19" ht="15.75" thickBot="1">
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="117"/>
+      <c r="D18" s="120"/>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>1000</v>
       </c>
-      <c r="G18" s="117" t="s">
+      <c r="G18" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="118"/>
-      <c r="J18" s="135" t="s">
+      <c r="H18" s="121"/>
+      <c r="J18" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="136"/>
-      <c r="L18" s="135" t="s">
+      <c r="K18" s="162"/>
+      <c r="L18" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="137"/>
-      <c r="N18" s="138"/>
-    </row>
-    <row r="19" spans="1:20">
+      <c r="M18" s="163"/>
+      <c r="N18" s="164"/>
+    </row>
+    <row r="19" spans="1:19">
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="117"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="3">
         <v>33.814022600000001</v>
       </c>
-      <c r="G19" s="117" t="s">
+      <c r="G19" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="118"/>
-    </row>
-    <row r="20" spans="1:20" ht="21.75" thickBot="1">
+      <c r="H19" s="121"/>
+    </row>
+    <row r="20" spans="1:19" ht="21.75" thickBot="1">
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="117"/>
+      <c r="D20" s="120"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="3">
         <v>0.26417205235800001</v>
       </c>
-      <c r="G20" s="117" t="s">
+      <c r="G20" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="118"/>
-      <c r="J20" s="146" t="s">
+      <c r="H20" s="121"/>
+      <c r="J20" s="131" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="146"/>
-      <c r="L20" s="147" t="s">
+      <c r="K20" s="131"/>
+      <c r="L20" s="132" t="s">
         <v>130</v>
       </c>
-      <c r="M20" s="148"/>
-      <c r="N20" s="148"/>
-    </row>
-    <row r="21" spans="1:20">
+      <c r="M20" s="133"/>
+      <c r="N20" s="133"/>
+    </row>
+    <row r="21" spans="1:19">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="117"/>
+      <c r="D21" s="120"/>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="3">
         <v>4.9289199999999997</v>
       </c>
-      <c r="G21" s="117" t="s">
+      <c r="G21" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="118"/>
-      <c r="M21" s="91">
+      <c r="H21" s="121"/>
+      <c r="M21" s="89">
         <v>15</v>
       </c>
-      <c r="N21" s="141" t="s">
+      <c r="N21" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="O21" s="141"/>
-      <c r="P21" s="141"/>
-      <c r="Q21" s="141"/>
-      <c r="R21" s="142"/>
-    </row>
-    <row r="22" spans="1:20" ht="15.6" customHeight="1">
+      <c r="O21" s="126"/>
+      <c r="P21" s="126"/>
+      <c r="Q21" s="126"/>
+      <c r="R21" s="127"/>
+    </row>
+    <row r="22" spans="1:19" ht="15.6" customHeight="1">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="117" t="s">
+      <c r="C22" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="117"/>
+      <c r="D22" s="120"/>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>3.28084</v>
       </c>
-      <c r="G22" s="117" t="s">
+      <c r="G22" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="118"/>
-      <c r="M22" s="93">
+      <c r="H22" s="121"/>
+      <c r="M22" s="91">
         <v>15</v>
       </c>
-      <c r="N22" s="163" t="s">
+      <c r="N22" s="122" t="s">
         <v>42</v>
       </c>
-      <c r="O22" s="163"/>
-      <c r="P22" s="163"/>
-      <c r="Q22" s="163"/>
-      <c r="R22" s="164"/>
-    </row>
-    <row r="23" spans="1:20" ht="15.6" customHeight="1" thickBot="1">
+      <c r="O22" s="122"/>
+      <c r="P22" s="122"/>
+      <c r="Q22" s="122"/>
+      <c r="R22" s="123"/>
+    </row>
+    <row r="23" spans="1:19" ht="15.6" customHeight="1" thickBot="1">
       <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="129" t="s">
+      <c r="C23" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="129"/>
+      <c r="D23" s="155"/>
       <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="5">
         <v>24</v>
       </c>
-      <c r="G23" s="129" t="s">
+      <c r="G23" s="155" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="130"/>
-      <c r="M23" s="94">
+      <c r="H23" s="156"/>
+      <c r="M23" s="92">
         <v>16</v>
       </c>
-      <c r="N23" s="139" t="s">
+      <c r="N23" s="124" t="s">
         <v>44</v>
       </c>
-      <c r="O23" s="139"/>
-      <c r="P23" s="139"/>
-      <c r="Q23" s="139"/>
-      <c r="R23" s="140"/>
-    </row>
-    <row r="24" spans="1:20" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A24" s="149" t="s">
+      <c r="O23" s="124"/>
+      <c r="P23" s="124"/>
+      <c r="Q23" s="124"/>
+      <c r="R23" s="125"/>
+    </row>
+    <row r="24" spans="1:19" ht="15.6" customHeight="1" thickBot="1">
+      <c r="A24" s="134" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="150"/>
-      <c r="C24" s="150"/>
-      <c r="D24" s="150"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="150"/>
-      <c r="K24" s="151"/>
-      <c r="M24" s="92">
+      <c r="B24" s="135"/>
+      <c r="C24" s="135"/>
+      <c r="D24" s="135"/>
+      <c r="E24" s="135"/>
+      <c r="F24" s="135"/>
+      <c r="G24" s="135"/>
+      <c r="H24" s="135"/>
+      <c r="I24" s="135"/>
+      <c r="J24" s="135"/>
+      <c r="K24" s="136"/>
+      <c r="M24" s="90">
         <v>16</v>
       </c>
-      <c r="N24" s="161" t="s">
+      <c r="N24" s="146" t="s">
         <v>132</v>
       </c>
-      <c r="O24" s="161"/>
-      <c r="P24" s="161"/>
-      <c r="Q24" s="161"/>
-      <c r="R24" s="162"/>
-      <c r="S24" s="95"/>
-      <c r="T24" s="96"/>
-    </row>
-    <row r="25" spans="1:20" ht="15.75" hidden="1" thickBot="1">
-      <c r="A25" s="152"/>
-      <c r="B25" s="153"/>
-      <c r="C25" s="153"/>
-      <c r="D25" s="153"/>
-      <c r="E25" s="153"/>
-      <c r="F25" s="153"/>
-      <c r="G25" s="153"/>
-      <c r="H25" s="153"/>
-      <c r="I25" s="153"/>
-      <c r="J25" s="153"/>
-      <c r="K25" s="154"/>
-      <c r="M25" s="83">
+      <c r="O24" s="146"/>
+      <c r="P24" s="146"/>
+      <c r="Q24" s="146"/>
+      <c r="R24" s="147"/>
+      <c r="S24" s="93"/>
+    </row>
+    <row r="25" spans="1:19" ht="15.75" hidden="1" thickBot="1">
+      <c r="A25" s="137"/>
+      <c r="B25" s="138"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="138"/>
+      <c r="F25" s="138"/>
+      <c r="G25" s="138"/>
+      <c r="H25" s="138"/>
+      <c r="I25" s="138"/>
+      <c r="J25" s="138"/>
+      <c r="K25" s="139"/>
+      <c r="M25" s="82">
         <v>16</v>
       </c>
-      <c r="N25" s="143" t="s">
+      <c r="N25" s="128" t="s">
         <v>45</v>
       </c>
-      <c r="O25" s="144"/>
-      <c r="P25" s="144"/>
-      <c r="Q25" s="144"/>
-      <c r="R25" s="145"/>
-    </row>
-    <row r="26" spans="1:20" hidden="1">
-      <c r="A26" s="152"/>
-      <c r="B26" s="153"/>
-      <c r="C26" s="153"/>
-      <c r="D26" s="153"/>
-      <c r="E26" s="153"/>
-      <c r="F26" s="153"/>
-      <c r="G26" s="153"/>
-      <c r="H26" s="153"/>
-      <c r="I26" s="153"/>
-      <c r="J26" s="153"/>
-      <c r="K26" s="154"/>
-    </row>
-    <row r="27" spans="1:20" hidden="1">
-      <c r="A27" s="152"/>
-      <c r="B27" s="153"/>
-      <c r="C27" s="153"/>
-      <c r="D27" s="153"/>
-      <c r="E27" s="153"/>
-      <c r="F27" s="153"/>
-      <c r="G27" s="153"/>
-      <c r="H27" s="153"/>
-      <c r="I27" s="153"/>
-      <c r="J27" s="153"/>
-      <c r="K27" s="154"/>
-    </row>
-    <row r="28" spans="1:20" hidden="1">
-      <c r="A28" s="152"/>
-      <c r="B28" s="153"/>
-      <c r="C28" s="153"/>
-      <c r="D28" s="153"/>
-      <c r="E28" s="153"/>
-      <c r="F28" s="153"/>
-      <c r="G28" s="153"/>
-      <c r="H28" s="153"/>
-      <c r="I28" s="153"/>
-      <c r="J28" s="153"/>
-      <c r="K28" s="154"/>
-    </row>
-    <row r="29" spans="1:20" hidden="1">
-      <c r="A29" s="152"/>
-      <c r="B29" s="153"/>
-      <c r="C29" s="153"/>
-      <c r="D29" s="153"/>
-      <c r="E29" s="153"/>
-      <c r="F29" s="153"/>
-      <c r="G29" s="153"/>
-      <c r="H29" s="153"/>
-      <c r="I29" s="153"/>
-      <c r="J29" s="153"/>
-      <c r="K29" s="154"/>
-    </row>
-    <row r="30" spans="1:20" hidden="1">
-      <c r="A30" s="152"/>
-      <c r="B30" s="153"/>
-      <c r="C30" s="153"/>
-      <c r="D30" s="153"/>
-      <c r="E30" s="153"/>
-      <c r="F30" s="153"/>
-      <c r="G30" s="153"/>
-      <c r="H30" s="153"/>
-      <c r="I30" s="153"/>
-      <c r="J30" s="153"/>
-      <c r="K30" s="154"/>
-    </row>
-    <row r="31" spans="1:20" ht="116.25" customHeight="1" thickBot="1">
-      <c r="A31" s="155"/>
-      <c r="B31" s="156"/>
-      <c r="C31" s="156"/>
-      <c r="D31" s="156"/>
-      <c r="E31" s="156"/>
-      <c r="F31" s="156"/>
-      <c r="G31" s="156"/>
-      <c r="H31" s="156"/>
-      <c r="I31" s="156"/>
-      <c r="J31" s="156"/>
-      <c r="K31" s="157"/>
-      <c r="M31" s="158" t="s">
+      <c r="O25" s="129"/>
+      <c r="P25" s="129"/>
+      <c r="Q25" s="129"/>
+      <c r="R25" s="130"/>
+    </row>
+    <row r="26" spans="1:19" hidden="1">
+      <c r="A26" s="137"/>
+      <c r="B26" s="138"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="138"/>
+      <c r="F26" s="138"/>
+      <c r="G26" s="138"/>
+      <c r="H26" s="138"/>
+      <c r="I26" s="138"/>
+      <c r="J26" s="138"/>
+      <c r="K26" s="139"/>
+    </row>
+    <row r="27" spans="1:19" hidden="1">
+      <c r="A27" s="137"/>
+      <c r="B27" s="138"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
+      <c r="G27" s="138"/>
+      <c r="H27" s="138"/>
+      <c r="I27" s="138"/>
+      <c r="J27" s="138"/>
+      <c r="K27" s="139"/>
+    </row>
+    <row r="28" spans="1:19" hidden="1">
+      <c r="A28" s="137"/>
+      <c r="B28" s="138"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="138"/>
+      <c r="F28" s="138"/>
+      <c r="G28" s="138"/>
+      <c r="H28" s="138"/>
+      <c r="I28" s="138"/>
+      <c r="J28" s="138"/>
+      <c r="K28" s="139"/>
+    </row>
+    <row r="29" spans="1:19" hidden="1">
+      <c r="A29" s="137"/>
+      <c r="B29" s="138"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="138"/>
+      <c r="F29" s="138"/>
+      <c r="G29" s="138"/>
+      <c r="H29" s="138"/>
+      <c r="I29" s="138"/>
+      <c r="J29" s="138"/>
+      <c r="K29" s="139"/>
+    </row>
+    <row r="30" spans="1:19" hidden="1">
+      <c r="A30" s="137"/>
+      <c r="B30" s="138"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="138"/>
+      <c r="G30" s="138"/>
+      <c r="H30" s="138"/>
+      <c r="I30" s="138"/>
+      <c r="J30" s="138"/>
+      <c r="K30" s="139"/>
+    </row>
+    <row r="31" spans="1:19" ht="116.25" customHeight="1" thickBot="1">
+      <c r="A31" s="140"/>
+      <c r="B31" s="141"/>
+      <c r="C31" s="141"/>
+      <c r="D31" s="141"/>
+      <c r="E31" s="141"/>
+      <c r="F31" s="141"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="141"/>
+      <c r="I31" s="141"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="142"/>
+      <c r="M31" s="143" t="s">
         <v>133</v>
       </c>
-      <c r="N31" s="159"/>
-      <c r="O31" s="159"/>
-      <c r="P31" s="159"/>
-      <c r="Q31" s="159"/>
-      <c r="R31" s="160"/>
-    </row>
-    <row r="32" spans="1:20" ht="17.100000000000001" customHeight="1" thickBot="1">
+      <c r="N31" s="144"/>
+      <c r="O31" s="144"/>
+      <c r="P31" s="144"/>
+      <c r="Q31" s="144"/>
+      <c r="R31" s="145"/>
+    </row>
+    <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A32" s="11"/>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
@@ -3482,29 +3472,26 @@
       <c r="K32" s="10"/>
     </row>
     <row r="33" spans="1:17" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A33" s="77"/>
-      <c r="B33" s="84"/>
-      <c r="C33" s="84"/>
-      <c r="D33" s="84"/>
-      <c r="E33" s="84"/>
-      <c r="F33" s="209" t="s">
+      <c r="B33" s="83"/>
+      <c r="C33" s="83"/>
+      <c r="D33" s="83"/>
+      <c r="E33" s="83"/>
+      <c r="F33" s="103" t="s">
         <v>134</v>
       </c>
-      <c r="G33" s="210"/>
-      <c r="H33" s="210"/>
-      <c r="I33" s="210"/>
-      <c r="J33" s="210"/>
-      <c r="K33" s="210"/>
-      <c r="L33" s="210"/>
-      <c r="M33" s="210"/>
-      <c r="N33" s="210"/>
-      <c r="O33" s="210"/>
-      <c r="P33" s="211"/>
-      <c r="Q33" s="77"/>
+      <c r="G33" s="104"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="104"/>
+      <c r="J33" s="104"/>
+      <c r="K33" s="104"/>
+      <c r="L33" s="104"/>
+      <c r="M33" s="104"/>
+      <c r="N33" s="104"/>
+      <c r="O33" s="104"/>
+      <c r="P33" s="105"/>
     </row>
     <row r="34" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A34" s="89"/>
-      <c r="B34" s="90"/>
+      <c r="B34" s="88"/>
       <c r="C34" s="47" t="s">
         <v>47</v>
       </c>
@@ -3514,16 +3501,16 @@
       <c r="E34" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F34" s="85" t="s">
+      <c r="F34" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="G34" s="86" t="s">
+      <c r="G34" s="85" t="s">
         <v>51</v>
       </c>
       <c r="H34" s="30" t="s">
         <v>49</v>
       </c>
-      <c r="I34" s="87" t="s">
+      <c r="I34" s="86" t="s">
         <v>52</v>
       </c>
       <c r="J34" s="30" t="s">
@@ -3544,16 +3531,16 @@
       <c r="O34" s="30" t="s">
         <v>54</v>
       </c>
-      <c r="P34" s="88" t="s">
+      <c r="P34" s="87" t="s">
         <v>55</v>
       </c>
-      <c r="Q34" s="78"/>
+      <c r="Q34" s="77"/>
     </row>
     <row r="35" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A35" s="176" t="s">
+      <c r="A35" s="117" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="178"/>
+      <c r="B35" s="119"/>
       <c r="C35" s="62">
         <v>25</v>
       </c>
@@ -3580,9 +3567,9 @@
       <c r="J35" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="175"/>
-      <c r="L35" s="175"/>
-      <c r="M35" s="175"/>
+      <c r="K35" s="116"/>
+      <c r="L35" s="116"/>
+      <c r="M35" s="116"/>
       <c r="N35" s="64" t="s">
         <v>10</v>
       </c>
@@ -3593,13 +3580,13 @@
       <c r="P35" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="Q35" s="78"/>
+      <c r="Q35" s="77"/>
     </row>
     <row r="36" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A36" s="176" t="s">
+      <c r="A36" s="117" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="177"/>
+      <c r="B36" s="118"/>
       <c r="C36" s="62">
         <v>2.5</v>
       </c>
@@ -3616,21 +3603,21 @@
       </c>
       <c r="I36" s="61"/>
       <c r="J36" s="65"/>
-      <c r="K36" s="175"/>
-      <c r="L36" s="175"/>
-      <c r="M36" s="175"/>
+      <c r="K36" s="116"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="116"/>
       <c r="N36" s="64" t="s">
         <v>10</v>
       </c>
       <c r="O36" s="61"/>
       <c r="P36" s="66"/>
-      <c r="Q36" s="78"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A37" s="173" t="s">
+      <c r="A37" s="114" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="174"/>
+      <c r="B37" s="115"/>
       <c r="C37" s="62">
         <v>5</v>
       </c>
@@ -3660,28 +3647,28 @@
       <c r="Q37" s="75"/>
     </row>
     <row r="38" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A38" s="167" t="s">
+      <c r="A38" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="168"/>
-      <c r="C38" s="169"/>
-      <c r="D38" s="169"/>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="169"/>
-      <c r="I38" s="169"/>
-      <c r="J38" s="169"/>
-      <c r="K38" s="169"/>
-      <c r="L38" s="169"/>
-      <c r="M38" s="169"/>
-      <c r="N38" s="169"/>
-      <c r="O38" s="169"/>
-      <c r="P38" s="170"/>
+      <c r="B38" s="109"/>
+      <c r="C38" s="110"/>
+      <c r="D38" s="110"/>
+      <c r="E38" s="110"/>
+      <c r="F38" s="110"/>
+      <c r="G38" s="110"/>
+      <c r="H38" s="110"/>
+      <c r="I38" s="110"/>
+      <c r="J38" s="110"/>
+      <c r="K38" s="110"/>
+      <c r="L38" s="110"/>
+      <c r="M38" s="110"/>
+      <c r="N38" s="110"/>
+      <c r="O38" s="110"/>
+      <c r="P38" s="111"/>
     </row>
     <row r="39" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A39" s="171"/>
-      <c r="B39" s="172"/>
+      <c r="A39" s="112"/>
+      <c r="B39" s="113"/>
       <c r="C39" s="18" t="s">
         <v>47</v>
       </c>
@@ -3726,10 +3713,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A40" s="176" t="s">
+      <c r="A40" s="117" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="177"/>
+      <c r="B40" s="118"/>
       <c r="C40" s="62" t="str">
         <f>IF(L$20="Your Name!", "Enter Name in L20",ROUND(50*Random!D21,1)+1)</f>
         <v>Enter Name in L20</v>
@@ -3747,9 +3734,9 @@
       </c>
       <c r="I40" s="61"/>
       <c r="J40" s="65"/>
-      <c r="K40" s="175"/>
-      <c r="L40" s="175"/>
-      <c r="M40" s="175"/>
+      <c r="K40" s="116"/>
+      <c r="L40" s="116"/>
+      <c r="M40" s="116"/>
       <c r="N40" s="64" t="s">
         <v>10</v>
       </c>
@@ -3757,10 +3744,10 @@
       <c r="P40" s="66"/>
     </row>
     <row r="41" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A41" s="165" t="s">
+      <c r="A41" s="106" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="166"/>
+      <c r="B41" s="107"/>
       <c r="C41" s="62" t="str">
         <f>IF(L$20="Your Name!", "Enter Name in L20",ROUND(50*Random!D22,1)+1)</f>
         <v>Enter Name in L20</v>
@@ -3771,55 +3758,39 @@
       <c r="E41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="F41" s="79"/>
-      <c r="G41" s="80"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="79"/>
       <c r="H41" s="67" t="s">
         <v>49</v>
       </c>
       <c r="I41" s="61"/>
-      <c r="J41" s="80"/>
+      <c r="J41" s="79"/>
       <c r="K41" s="67" t="s">
         <v>49</v>
       </c>
-      <c r="L41" s="79"/>
-      <c r="M41" s="80"/>
+      <c r="L41" s="78"/>
+      <c r="M41" s="79"/>
       <c r="N41" s="67" t="s">
         <v>10</v>
       </c>
-      <c r="O41" s="81"/>
-      <c r="P41" s="82"/>
+      <c r="O41" s="80"/>
+      <c r="P41" s="81"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="dB23+XZH+Oa0Huu6tUAJA79GWafRoG1zQyItfVAWpUgqFL4v2gk8yvHQ7YMxAU8GJxGPHpCzDU7yRz0ujc0p5g==" saltValue="7CvP4XnLWnuOI8Pc8+HWBw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="xYqynVFXRMtypzOki6E0FV5yKOx/aoNLP8FgcPBcwCZsd4S5Oy7xfUbX4GJVBEIXYivvt9V29puYFCTvDAmUog==" saltValue="5Rp3rBS2Sr8XjSzk2FSxgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="56">
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="N22:R22"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="N23:R23"/>
-    <mergeCell ref="N21:R21"/>
-    <mergeCell ref="N25:R25"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="A24:K31"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="M31:R31"/>
-    <mergeCell ref="N24:R24"/>
+    <mergeCell ref="A1:P11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L14:N14"/>
     <mergeCell ref="J15:K15"/>
@@ -3836,18 +3807,34 @@
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="A1:P11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="N23:R23"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="N25:R25"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="A24:K31"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M31:R31"/>
+    <mergeCell ref="N24:R24"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="N22:R22"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <conditionalFormatting sqref="F36:F37 I36:I37 O36:O37 L37 F40:F41 I40:I41 O40:O41 L41">
     <cfRule type="expression" dxfId="2" priority="2">
@@ -5930,590 +5917,590 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="165" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="107"/>
-      <c r="H1" s="107"/>
-      <c r="I1" s="107"/>
-      <c r="J1" s="107"/>
-      <c r="K1" s="107"/>
-      <c r="L1" s="107"/>
-      <c r="M1" s="107"/>
-      <c r="N1" s="107"/>
-      <c r="O1" s="107"/>
-      <c r="P1" s="108"/>
+      <c r="B1" s="166"/>
+      <c r="C1" s="166"/>
+      <c r="D1" s="166"/>
+      <c r="E1" s="166"/>
+      <c r="F1" s="166"/>
+      <c r="G1" s="166"/>
+      <c r="H1" s="166"/>
+      <c r="I1" s="166"/>
+      <c r="J1" s="166"/>
+      <c r="K1" s="166"/>
+      <c r="L1" s="166"/>
+      <c r="M1" s="166"/>
+      <c r="N1" s="166"/>
+      <c r="O1" s="166"/>
+      <c r="P1" s="167"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="109"/>
-      <c r="B2" s="110"/>
-      <c r="C2" s="110"/>
-      <c r="D2" s="110"/>
-      <c r="E2" s="110"/>
-      <c r="F2" s="110"/>
-      <c r="G2" s="110"/>
-      <c r="H2" s="110"/>
-      <c r="I2" s="110"/>
-      <c r="J2" s="110"/>
-      <c r="K2" s="110"/>
-      <c r="L2" s="110"/>
-      <c r="M2" s="110"/>
-      <c r="N2" s="110"/>
-      <c r="O2" s="110"/>
-      <c r="P2" s="111"/>
+      <c r="A2" s="168"/>
+      <c r="B2" s="169"/>
+      <c r="C2" s="169"/>
+      <c r="D2" s="169"/>
+      <c r="E2" s="169"/>
+      <c r="F2" s="169"/>
+      <c r="G2" s="169"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
+      <c r="J2" s="169"/>
+      <c r="K2" s="169"/>
+      <c r="L2" s="169"/>
+      <c r="M2" s="169"/>
+      <c r="N2" s="169"/>
+      <c r="O2" s="169"/>
+      <c r="P2" s="170"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="109"/>
-      <c r="B3" s="110"/>
-      <c r="C3" s="110"/>
-      <c r="D3" s="110"/>
-      <c r="E3" s="110"/>
-      <c r="F3" s="110"/>
-      <c r="G3" s="110"/>
-      <c r="H3" s="110"/>
-      <c r="I3" s="110"/>
-      <c r="J3" s="110"/>
-      <c r="K3" s="110"/>
-      <c r="L3" s="110"/>
-      <c r="M3" s="110"/>
-      <c r="N3" s="110"/>
-      <c r="O3" s="110"/>
-      <c r="P3" s="111"/>
+      <c r="A3" s="168"/>
+      <c r="B3" s="169"/>
+      <c r="C3" s="169"/>
+      <c r="D3" s="169"/>
+      <c r="E3" s="169"/>
+      <c r="F3" s="169"/>
+      <c r="G3" s="169"/>
+      <c r="H3" s="169"/>
+      <c r="I3" s="169"/>
+      <c r="J3" s="169"/>
+      <c r="K3" s="169"/>
+      <c r="L3" s="169"/>
+      <c r="M3" s="169"/>
+      <c r="N3" s="169"/>
+      <c r="O3" s="169"/>
+      <c r="P3" s="170"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="109"/>
-      <c r="B4" s="110"/>
-      <c r="C4" s="110"/>
-      <c r="D4" s="110"/>
-      <c r="E4" s="110"/>
-      <c r="F4" s="110"/>
-      <c r="G4" s="110"/>
-      <c r="H4" s="110"/>
-      <c r="I4" s="110"/>
-      <c r="J4" s="110"/>
-      <c r="K4" s="110"/>
-      <c r="L4" s="110"/>
-      <c r="M4" s="110"/>
-      <c r="N4" s="110"/>
-      <c r="O4" s="110"/>
-      <c r="P4" s="111"/>
+      <c r="A4" s="168"/>
+      <c r="B4" s="169"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="170"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="109"/>
-      <c r="B5" s="110"/>
-      <c r="C5" s="110"/>
-      <c r="D5" s="110"/>
-      <c r="E5" s="110"/>
-      <c r="F5" s="110"/>
-      <c r="G5" s="110"/>
-      <c r="H5" s="110"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
-      <c r="N5" s="110"/>
-      <c r="O5" s="110"/>
-      <c r="P5" s="111"/>
+      <c r="A5" s="168"/>
+      <c r="B5" s="169"/>
+      <c r="C5" s="169"/>
+      <c r="D5" s="169"/>
+      <c r="E5" s="169"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="169"/>
+      <c r="H5" s="169"/>
+      <c r="I5" s="169"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="169"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="169"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+      <c r="P5" s="170"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="109"/>
-      <c r="B6" s="110"/>
-      <c r="C6" s="110"/>
-      <c r="D6" s="110"/>
-      <c r="E6" s="110"/>
-      <c r="F6" s="110"/>
-      <c r="G6" s="110"/>
-      <c r="H6" s="110"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110"/>
-      <c r="M6" s="110"/>
-      <c r="N6" s="110"/>
-      <c r="O6" s="110"/>
-      <c r="P6" s="111"/>
+      <c r="A6" s="168"/>
+      <c r="B6" s="169"/>
+      <c r="C6" s="169"/>
+      <c r="D6" s="169"/>
+      <c r="E6" s="169"/>
+      <c r="F6" s="169"/>
+      <c r="G6" s="169"/>
+      <c r="H6" s="169"/>
+      <c r="I6" s="169"/>
+      <c r="J6" s="169"/>
+      <c r="K6" s="169"/>
+      <c r="L6" s="169"/>
+      <c r="M6" s="169"/>
+      <c r="N6" s="169"/>
+      <c r="O6" s="169"/>
+      <c r="P6" s="170"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="109"/>
-      <c r="B7" s="110"/>
-      <c r="C7" s="110"/>
-      <c r="D7" s="110"/>
-      <c r="E7" s="110"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="110"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110"/>
-      <c r="M7" s="110"/>
-      <c r="N7" s="110"/>
-      <c r="O7" s="110"/>
-      <c r="P7" s="111"/>
+      <c r="A7" s="168"/>
+      <c r="B7" s="169"/>
+      <c r="C7" s="169"/>
+      <c r="D7" s="169"/>
+      <c r="E7" s="169"/>
+      <c r="F7" s="169"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="169"/>
+      <c r="I7" s="169"/>
+      <c r="J7" s="169"/>
+      <c r="K7" s="169"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="169"/>
+      <c r="N7" s="169"/>
+      <c r="O7" s="169"/>
+      <c r="P7" s="170"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="109"/>
-      <c r="B8" s="110"/>
-      <c r="C8" s="110"/>
-      <c r="D8" s="110"/>
-      <c r="E8" s="110"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="110"/>
-      <c r="H8" s="110"/>
-      <c r="I8" s="110"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="110"/>
-      <c r="P8" s="111"/>
+      <c r="A8" s="168"/>
+      <c r="B8" s="169"/>
+      <c r="C8" s="169"/>
+      <c r="D8" s="169"/>
+      <c r="E8" s="169"/>
+      <c r="F8" s="169"/>
+      <c r="G8" s="169"/>
+      <c r="H8" s="169"/>
+      <c r="I8" s="169"/>
+      <c r="J8" s="169"/>
+      <c r="K8" s="169"/>
+      <c r="L8" s="169"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+      <c r="P8" s="170"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="109"/>
-      <c r="B9" s="110"/>
-      <c r="C9" s="110"/>
-      <c r="D9" s="110"/>
-      <c r="E9" s="110"/>
-      <c r="F9" s="110"/>
-      <c r="G9" s="110"/>
-      <c r="H9" s="110"/>
-      <c r="I9" s="110"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="110"/>
-      <c r="N9" s="110"/>
-      <c r="O9" s="110"/>
-      <c r="P9" s="111"/>
+      <c r="A9" s="168"/>
+      <c r="B9" s="169"/>
+      <c r="C9" s="169"/>
+      <c r="D9" s="169"/>
+      <c r="E9" s="169"/>
+      <c r="F9" s="169"/>
+      <c r="G9" s="169"/>
+      <c r="H9" s="169"/>
+      <c r="I9" s="169"/>
+      <c r="J9" s="169"/>
+      <c r="K9" s="169"/>
+      <c r="L9" s="169"/>
+      <c r="M9" s="169"/>
+      <c r="N9" s="169"/>
+      <c r="O9" s="169"/>
+      <c r="P9" s="170"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="109"/>
-      <c r="B10" s="110"/>
-      <c r="C10" s="110"/>
-      <c r="D10" s="110"/>
-      <c r="E10" s="110"/>
-      <c r="F10" s="110"/>
-      <c r="G10" s="110"/>
-      <c r="H10" s="110"/>
-      <c r="I10" s="110"/>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="110"/>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110"/>
-      <c r="P10" s="111"/>
+      <c r="A10" s="168"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="169"/>
+      <c r="D10" s="169"/>
+      <c r="E10" s="169"/>
+      <c r="F10" s="169"/>
+      <c r="G10" s="169"/>
+      <c r="H10" s="169"/>
+      <c r="I10" s="169"/>
+      <c r="J10" s="169"/>
+      <c r="K10" s="169"/>
+      <c r="L10" s="169"/>
+      <c r="M10" s="169"/>
+      <c r="N10" s="169"/>
+      <c r="O10" s="169"/>
+      <c r="P10" s="170"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A11" s="112"/>
-      <c r="B11" s="113"/>
-      <c r="C11" s="113"/>
-      <c r="D11" s="113"/>
-      <c r="E11" s="113"/>
-      <c r="F11" s="113"/>
-      <c r="G11" s="113"/>
-      <c r="H11" s="113"/>
-      <c r="I11" s="113"/>
-      <c r="J11" s="113"/>
-      <c r="K11" s="113"/>
-      <c r="L11" s="113"/>
-      <c r="M11" s="113"/>
-      <c r="N11" s="113"/>
-      <c r="O11" s="113"/>
-      <c r="P11" s="114"/>
+      <c r="A11" s="171"/>
+      <c r="B11" s="172"/>
+      <c r="C11" s="172"/>
+      <c r="D11" s="172"/>
+      <c r="E11" s="172"/>
+      <c r="F11" s="172"/>
+      <c r="G11" s="172"/>
+      <c r="H11" s="172"/>
+      <c r="I11" s="172"/>
+      <c r="J11" s="172"/>
+      <c r="K11" s="172"/>
+      <c r="L11" s="172"/>
+      <c r="M11" s="172"/>
+      <c r="N11" s="172"/>
+      <c r="O11" s="172"/>
+      <c r="P11" s="173"/>
     </row>
     <row r="12" spans="1:16" ht="30.75" thickBot="1">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="115" t="s">
+      <c r="C12" s="174" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="115"/>
+      <c r="D12" s="174"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="115" t="s">
+      <c r="G12" s="174" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="116"/>
+      <c r="H12" s="175"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="117" t="s">
+      <c r="C13" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="117"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>2.2046199999999998</v>
       </c>
-      <c r="G13" s="117" t="s">
+      <c r="G13" s="120" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="118"/>
-      <c r="J13" s="119" t="s">
+      <c r="H13" s="121"/>
+      <c r="J13" s="176" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="120"/>
-      <c r="L13" s="120"/>
-      <c r="M13" s="120"/>
-      <c r="N13" s="121"/>
+      <c r="K13" s="177"/>
+      <c r="L13" s="177"/>
+      <c r="M13" s="177"/>
+      <c r="N13" s="178"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="117" t="s">
+      <c r="C14" s="120" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="117"/>
+      <c r="D14" s="120"/>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
         <v>29.573499999999999</v>
       </c>
-      <c r="G14" s="117" t="s">
+      <c r="G14" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="118"/>
-      <c r="J14" s="122" t="s">
+      <c r="H14" s="121"/>
+      <c r="J14" s="148" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="123"/>
-      <c r="L14" s="122" t="s">
+      <c r="K14" s="149"/>
+      <c r="L14" s="148" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="117"/>
-      <c r="N14" s="118"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="121"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="117" t="s">
+      <c r="C15" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="117"/>
+      <c r="D15" s="120"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3">
         <v>28.349523125000001</v>
       </c>
-      <c r="G15" s="117" t="s">
+      <c r="G15" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="118"/>
-      <c r="J15" s="124" t="s">
+      <c r="H15" s="121"/>
+      <c r="J15" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="125"/>
-      <c r="L15" s="126" t="s">
+      <c r="K15" s="151"/>
+      <c r="L15" s="152" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="127"/>
-      <c r="N15" s="128"/>
+      <c r="M15" s="153"/>
+      <c r="N15" s="154"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="117" t="s">
+      <c r="C16" s="120" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="117"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2">
         <v>1000</v>
       </c>
-      <c r="G16" s="117" t="s">
+      <c r="G16" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="118"/>
-      <c r="J16" s="131" t="s">
+      <c r="H16" s="121"/>
+      <c r="J16" s="157" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="132"/>
-      <c r="L16" s="126" t="s">
+      <c r="K16" s="158"/>
+      <c r="L16" s="152" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="127"/>
-      <c r="N16" s="128"/>
+      <c r="M16" s="153"/>
+      <c r="N16" s="154"/>
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="117" t="s">
+      <c r="C17" s="120" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="117"/>
+      <c r="D17" s="120"/>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
         <v>1000</v>
       </c>
-      <c r="G17" s="117" t="s">
+      <c r="G17" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="118"/>
-      <c r="J17" s="133" t="s">
+      <c r="H17" s="121"/>
+      <c r="J17" s="159" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="134"/>
-      <c r="L17" s="126" t="s">
+      <c r="K17" s="160"/>
+      <c r="L17" s="152" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="127"/>
-      <c r="N17" s="128"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="154"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" thickBot="1">
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="117" t="s">
+      <c r="C18" s="120" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="117"/>
+      <c r="D18" s="120"/>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>1000</v>
       </c>
-      <c r="G18" s="117" t="s">
+      <c r="G18" s="120" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="118"/>
-      <c r="J18" s="135" t="s">
+      <c r="H18" s="121"/>
+      <c r="J18" s="161" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="136"/>
-      <c r="L18" s="135" t="s">
+      <c r="K18" s="162"/>
+      <c r="L18" s="161" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="137"/>
-      <c r="N18" s="138"/>
+      <c r="M18" s="163"/>
+      <c r="N18" s="164"/>
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="117" t="s">
+      <c r="C19" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="117"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="3">
         <v>33.814022600000001</v>
       </c>
-      <c r="G19" s="117" t="s">
+      <c r="G19" s="120" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="118"/>
+      <c r="H19" s="121"/>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="117" t="s">
+      <c r="C20" s="120" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="117"/>
+      <c r="D20" s="120"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="3">
         <v>0.26417205235800001</v>
       </c>
-      <c r="G20" s="117" t="s">
+      <c r="G20" s="120" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="118"/>
+      <c r="H20" s="121"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="117" t="s">
+      <c r="C21" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="117"/>
+      <c r="D21" s="120"/>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="3">
         <v>4.9289199999999997</v>
       </c>
-      <c r="G21" s="117" t="s">
+      <c r="G21" s="120" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="118"/>
+      <c r="H21" s="121"/>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="117" t="s">
+      <c r="C22" s="120" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="117"/>
+      <c r="D22" s="120"/>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>3.28084</v>
       </c>
-      <c r="G22" s="117" t="s">
+      <c r="G22" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="118"/>
+      <c r="H22" s="121"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="129" t="s">
+      <c r="C23" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="129"/>
+      <c r="D23" s="155"/>
       <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="5">
         <v>24</v>
       </c>
-      <c r="G23" s="129" t="s">
+      <c r="G23" s="155" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="130"/>
+      <c r="H23" s="156"/>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1">
-      <c r="A24" s="106" t="s">
+      <c r="A24" s="165" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="107"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="107"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="107"/>
-      <c r="G24" s="107"/>
-      <c r="H24" s="107"/>
-      <c r="I24" s="107"/>
-      <c r="J24" s="107"/>
-      <c r="K24" s="108"/>
+      <c r="B24" s="166"/>
+      <c r="C24" s="166"/>
+      <c r="D24" s="166"/>
+      <c r="E24" s="166"/>
+      <c r="F24" s="166"/>
+      <c r="G24" s="166"/>
+      <c r="H24" s="166"/>
+      <c r="I24" s="166"/>
+      <c r="J24" s="166"/>
+      <c r="K24" s="167"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="109"/>
-      <c r="B25" s="110"/>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="110"/>
-      <c r="I25" s="110"/>
-      <c r="J25" s="110"/>
-      <c r="K25" s="111"/>
+      <c r="A25" s="168"/>
+      <c r="B25" s="169"/>
+      <c r="C25" s="169"/>
+      <c r="D25" s="169"/>
+      <c r="E25" s="169"/>
+      <c r="F25" s="169"/>
+      <c r="G25" s="169"/>
+      <c r="H25" s="169"/>
+      <c r="I25" s="169"/>
+      <c r="J25" s="169"/>
+      <c r="K25" s="170"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="109"/>
-      <c r="B26" s="110"/>
-      <c r="C26" s="110"/>
-      <c r="D26" s="110"/>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
-      <c r="K26" s="111"/>
+      <c r="A26" s="168"/>
+      <c r="B26" s="169"/>
+      <c r="C26" s="169"/>
+      <c r="D26" s="169"/>
+      <c r="E26" s="169"/>
+      <c r="F26" s="169"/>
+      <c r="G26" s="169"/>
+      <c r="H26" s="169"/>
+      <c r="I26" s="169"/>
+      <c r="J26" s="169"/>
+      <c r="K26" s="170"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="109"/>
-      <c r="B27" s="110"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="110"/>
-      <c r="E27" s="110"/>
-      <c r="F27" s="110"/>
-      <c r="G27" s="110"/>
-      <c r="H27" s="110"/>
-      <c r="I27" s="110"/>
-      <c r="J27" s="110"/>
-      <c r="K27" s="111"/>
+      <c r="A27" s="168"/>
+      <c r="B27" s="169"/>
+      <c r="C27" s="169"/>
+      <c r="D27" s="169"/>
+      <c r="E27" s="169"/>
+      <c r="F27" s="169"/>
+      <c r="G27" s="169"/>
+      <c r="H27" s="169"/>
+      <c r="I27" s="169"/>
+      <c r="J27" s="169"/>
+      <c r="K27" s="170"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="109"/>
-      <c r="B28" s="110"/>
-      <c r="C28" s="110"/>
-      <c r="D28" s="110"/>
-      <c r="E28" s="110"/>
-      <c r="F28" s="110"/>
-      <c r="G28" s="110"/>
-      <c r="H28" s="110"/>
-      <c r="I28" s="110"/>
-      <c r="J28" s="110"/>
-      <c r="K28" s="111"/>
+      <c r="A28" s="168"/>
+      <c r="B28" s="169"/>
+      <c r="C28" s="169"/>
+      <c r="D28" s="169"/>
+      <c r="E28" s="169"/>
+      <c r="F28" s="169"/>
+      <c r="G28" s="169"/>
+      <c r="H28" s="169"/>
+      <c r="I28" s="169"/>
+      <c r="J28" s="169"/>
+      <c r="K28" s="170"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="109"/>
-      <c r="B29" s="110"/>
-      <c r="C29" s="110"/>
-      <c r="D29" s="110"/>
-      <c r="E29" s="110"/>
-      <c r="F29" s="110"/>
-      <c r="G29" s="110"/>
-      <c r="H29" s="110"/>
-      <c r="I29" s="110"/>
-      <c r="J29" s="110"/>
-      <c r="K29" s="111"/>
+      <c r="A29" s="168"/>
+      <c r="B29" s="169"/>
+      <c r="C29" s="169"/>
+      <c r="D29" s="169"/>
+      <c r="E29" s="169"/>
+      <c r="F29" s="169"/>
+      <c r="G29" s="169"/>
+      <c r="H29" s="169"/>
+      <c r="I29" s="169"/>
+      <c r="J29" s="169"/>
+      <c r="K29" s="170"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="109"/>
-      <c r="B30" s="110"/>
-      <c r="C30" s="110"/>
-      <c r="D30" s="110"/>
-      <c r="E30" s="110"/>
-      <c r="F30" s="110"/>
-      <c r="G30" s="110"/>
-      <c r="H30" s="110"/>
-      <c r="I30" s="110"/>
-      <c r="J30" s="110"/>
-      <c r="K30" s="111"/>
+      <c r="A30" s="168"/>
+      <c r="B30" s="169"/>
+      <c r="C30" s="169"/>
+      <c r="D30" s="169"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="169"/>
+      <c r="J30" s="169"/>
+      <c r="K30" s="170"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A31" s="112"/>
-      <c r="B31" s="113"/>
-      <c r="C31" s="113"/>
-      <c r="D31" s="113"/>
-      <c r="E31" s="113"/>
-      <c r="F31" s="113"/>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="114"/>
+      <c r="A31" s="171"/>
+      <c r="B31" s="172"/>
+      <c r="C31" s="172"/>
+      <c r="D31" s="172"/>
+      <c r="E31" s="172"/>
+      <c r="F31" s="172"/>
+      <c r="G31" s="172"/>
+      <c r="H31" s="172"/>
+      <c r="I31" s="172"/>
+      <c r="J31" s="172"/>
+      <c r="K31" s="173"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" thickBot="1">
       <c r="A32" s="11"/>
@@ -6529,28 +6516,28 @@
       <c r="K32" s="10"/>
     </row>
     <row r="33" spans="1:17" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A33" s="182" t="s">
+      <c r="A33" s="197" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="183"/>
-      <c r="C33" s="183"/>
-      <c r="D33" s="183"/>
-      <c r="E33" s="183"/>
-      <c r="F33" s="183"/>
-      <c r="G33" s="183"/>
-      <c r="H33" s="183"/>
-      <c r="I33" s="183"/>
-      <c r="J33" s="183"/>
-      <c r="K33" s="183"/>
-      <c r="L33" s="183"/>
-      <c r="M33" s="183"/>
-      <c r="N33" s="183"/>
-      <c r="O33" s="183"/>
-      <c r="P33" s="184"/>
+      <c r="B33" s="198"/>
+      <c r="C33" s="198"/>
+      <c r="D33" s="198"/>
+      <c r="E33" s="198"/>
+      <c r="F33" s="198"/>
+      <c r="G33" s="198"/>
+      <c r="H33" s="198"/>
+      <c r="I33" s="198"/>
+      <c r="J33" s="198"/>
+      <c r="K33" s="198"/>
+      <c r="L33" s="198"/>
+      <c r="M33" s="198"/>
+      <c r="N33" s="198"/>
+      <c r="O33" s="198"/>
+      <c r="P33" s="199"/>
     </row>
     <row r="34" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A34" s="185"/>
-      <c r="B34" s="186"/>
+      <c r="A34" s="190"/>
+      <c r="B34" s="191"/>
       <c r="C34" s="9" t="s">
         <v>47</v>
       </c>
@@ -6598,10 +6585,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="45.75" customHeight="1" thickBot="1">
-      <c r="A35" s="179" t="s">
+      <c r="A35" s="194" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="180"/>
+      <c r="B35" s="195"/>
       <c r="C35" s="14">
         <v>25</v>
       </c>
@@ -6628,9 +6615,9 @@
       <c r="J35" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="181"/>
-      <c r="L35" s="181"/>
-      <c r="M35" s="181"/>
+      <c r="K35" s="196"/>
+      <c r="L35" s="196"/>
+      <c r="M35" s="196"/>
       <c r="N35" s="35" t="s">
         <v>10</v>
       </c>
@@ -6646,10 +6633,10 @@
       </c>
     </row>
     <row r="36" spans="1:17" ht="33.950000000000003" customHeight="1" thickBot="1">
-      <c r="A36" s="189" t="s">
+      <c r="A36" s="181" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="190"/>
+      <c r="B36" s="182"/>
       <c r="C36" s="14">
         <v>2.5</v>
       </c>
@@ -6676,9 +6663,9 @@
       <c r="J36" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="K36" s="191"/>
-      <c r="L36" s="175"/>
-      <c r="M36" s="192"/>
+      <c r="K36" s="183"/>
+      <c r="L36" s="116"/>
+      <c r="M36" s="184"/>
       <c r="N36" s="35" t="s">
         <v>10</v>
       </c>
@@ -6692,10 +6679,10 @@
       <c r="Q36" s="12"/>
     </row>
     <row r="37" spans="1:17" ht="48.6" customHeight="1" thickBot="1">
-      <c r="A37" s="193" t="s">
+      <c r="A37" s="185" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="194"/>
+      <c r="B37" s="186"/>
       <c r="C37" s="14">
         <v>5</v>
       </c>
@@ -6745,28 +6732,28 @@
       <c r="Q37" s="13"/>
     </row>
     <row r="38" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A38" s="195" t="s">
+      <c r="A38" s="187" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="196"/>
-      <c r="C38" s="196"/>
-      <c r="D38" s="196"/>
-      <c r="E38" s="196"/>
-      <c r="F38" s="196"/>
-      <c r="G38" s="196"/>
-      <c r="H38" s="196"/>
-      <c r="I38" s="196"/>
-      <c r="J38" s="196"/>
-      <c r="K38" s="196"/>
-      <c r="L38" s="196"/>
-      <c r="M38" s="196"/>
-      <c r="N38" s="196"/>
-      <c r="O38" s="196"/>
-      <c r="P38" s="197"/>
+      <c r="B38" s="188"/>
+      <c r="C38" s="188"/>
+      <c r="D38" s="188"/>
+      <c r="E38" s="188"/>
+      <c r="F38" s="188"/>
+      <c r="G38" s="188"/>
+      <c r="H38" s="188"/>
+      <c r="I38" s="188"/>
+      <c r="J38" s="188"/>
+      <c r="K38" s="188"/>
+      <c r="L38" s="188"/>
+      <c r="M38" s="188"/>
+      <c r="N38" s="188"/>
+      <c r="O38" s="188"/>
+      <c r="P38" s="189"/>
     </row>
     <row r="39" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A39" s="185"/>
-      <c r="B39" s="186"/>
+      <c r="A39" s="190"/>
+      <c r="B39" s="191"/>
       <c r="C39" s="18" t="s">
         <v>47</v>
       </c>
@@ -6811,10 +6798,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="48.95" customHeight="1" thickBot="1">
-      <c r="A40" s="189" t="s">
+      <c r="A40" s="181" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="190"/>
+      <c r="B40" s="182"/>
       <c r="C40" s="19" t="str">
         <f>Conversions!C40</f>
         <v>Enter Name in L20</v>
@@ -6842,9 +6829,9 @@
       <c r="J40" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="K40" s="198"/>
-      <c r="L40" s="198"/>
-      <c r="M40" s="199"/>
+      <c r="K40" s="192"/>
+      <c r="L40" s="192"/>
+      <c r="M40" s="193"/>
       <c r="N40" s="26" t="s">
         <v>10</v>
       </c>
@@ -6857,10 +6844,10 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="48.95" customHeight="1" thickBot="1">
-      <c r="A41" s="187" t="s">
+      <c r="A41" s="179" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="188"/>
+      <c r="B41" s="180"/>
       <c r="C41" s="20" t="str">
         <f>Conversions!C41</f>
         <v>Enter Name in L20</v>
@@ -6911,14 +6898,34 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="A1:P11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C20:D20"/>
@@ -6932,34 +6939,14 @@
     <mergeCell ref="A24:K31"/>
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="A1:P11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:N13"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K40:M40"/>
   </mergeCells>
   <conditionalFormatting sqref="F40 I40">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7020,6 +7007,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -7236,15 +7232,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7256,6 +7243,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3B6B4C-EC0E-4746-BC50-2C3213BAC25B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75299CF-40C1-4653-959B-0AE66E133E77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7274,14 +7269,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3B6B4C-EC0E-4746-BC50-2C3213BAC25B}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D29BAF0-14B6-4E1B-BA72-51F7164DDA8E}">
   <ds:schemaRefs>

--- a/144/DQ Templates and Instructions/Topic 2 DQ 1/Topic 2 DQ 1.xlsx
+++ b/144/DQ Templates and Instructions/Topic 2 DQ 1/Topic 2 DQ 1.xlsx
@@ -8,18 +8,19 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gcumail.sharepoint.com/sites/MathematicsProgramFacultyStaff-MATOFTF/Shared Documents/MATOFTF/ALEKS/DQ Templates and Instructions/Topic 2 DQ 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="8_{EC0CA368-B35E-4E61-BE63-B68E8477FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D3808BB-37D4-41F7-8305-D783DD24AD34}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="8_{EC0CA368-B35E-4E61-BE63-B68E8477FF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03C9732A-F53B-4B47-BF4B-AC6581365416}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="30" windowWidth="23010" windowHeight="12210" activeTab="1" xr2:uid="{30DCFED0-AF9F-4763-8D9E-1F0E9BEB0013}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{30DCFED0-AF9F-4763-8D9E-1F0E9BEB0013}"/>
   </bookViews>
   <sheets>
     <sheet name="Goals and Instructions" sheetId="3" r:id="rId1"/>
     <sheet name="Conversions" sheetId="1" r:id="rId2"/>
-    <sheet name="Random" sheetId="5" state="hidden" r:id="rId3"/>
-    <sheet name="Solutions" sheetId="4" state="hidden" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId5"/>
+    <sheet name="Users" sheetId="6" state="hidden" r:id="rId3"/>
+    <sheet name="Random" sheetId="5" state="hidden" r:id="rId4"/>
+    <sheet name="Solutions" sheetId="4" state="hidden" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="2" state="hidden" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="137">
   <si>
     <t>Excel Skills Learned</t>
   </si>
@@ -574,6 +575,12 @@
   </si>
   <si>
     <t xml:space="preserve">Video explanations to follow along with A and B. </t>
+  </si>
+  <si>
+    <t>Names</t>
+  </si>
+  <si>
+    <t>Reset</t>
   </si>
 </sst>
 </file>
@@ -1454,7 +1461,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="209">
+  <cellXfs count="211">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1791,100 +1798,227 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -1894,323 +2028,203 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="35" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2709,63 +2723,63 @@
       <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="94" t="s">
+      <c r="D2" s="170" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="95"/>
-      <c r="F2" s="95"/>
-      <c r="G2" s="95"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="96"/>
+      <c r="E2" s="171"/>
+      <c r="F2" s="171"/>
+      <c r="G2" s="171"/>
+      <c r="H2" s="171"/>
+      <c r="I2" s="172"/>
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="97"/>
-      <c r="E3" s="98"/>
-      <c r="F3" s="98"/>
-      <c r="G3" s="98"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="99"/>
+      <c r="D3" s="173"/>
+      <c r="E3" s="174"/>
+      <c r="F3" s="174"/>
+      <c r="G3" s="174"/>
+      <c r="H3" s="174"/>
+      <c r="I3" s="175"/>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="97"/>
-      <c r="E4" s="98"/>
-      <c r="F4" s="98"/>
-      <c r="G4" s="98"/>
-      <c r="H4" s="98"/>
-      <c r="I4" s="99"/>
+      <c r="D4" s="173"/>
+      <c r="E4" s="174"/>
+      <c r="F4" s="174"/>
+      <c r="G4" s="174"/>
+      <c r="H4" s="174"/>
+      <c r="I4" s="175"/>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" s="53" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="97"/>
-      <c r="E5" s="98"/>
-      <c r="F5" s="98"/>
-      <c r="G5" s="98"/>
-      <c r="H5" s="98"/>
-      <c r="I5" s="99"/>
+      <c r="D5" s="173"/>
+      <c r="E5" s="174"/>
+      <c r="F5" s="174"/>
+      <c r="G5" s="174"/>
+      <c r="H5" s="174"/>
+      <c r="I5" s="175"/>
     </row>
     <row r="6" spans="2:9">
-      <c r="D6" s="97"/>
-      <c r="E6" s="98"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="98"/>
-      <c r="H6" s="98"/>
-      <c r="I6" s="99"/>
+      <c r="D6" s="173"/>
+      <c r="E6" s="174"/>
+      <c r="F6" s="174"/>
+      <c r="G6" s="174"/>
+      <c r="H6" s="174"/>
+      <c r="I6" s="175"/>
     </row>
     <row r="7" spans="2:9" ht="15.75" thickBot="1">
-      <c r="D7" s="100"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="102"/>
+      <c r="D7" s="176"/>
+      <c r="E7" s="177"/>
+      <c r="F7" s="177"/>
+      <c r="G7" s="177"/>
+      <c r="H7" s="177"/>
+      <c r="I7" s="178"/>
     </row>
     <row r="8" spans="2:9" ht="19.5" thickBot="1">
       <c r="B8" s="52" t="s">
@@ -2805,658 +2819,658 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
-      <c r="M1" s="166"/>
-      <c r="N1" s="166"/>
-      <c r="O1" s="166"/>
-      <c r="P1" s="167"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="96"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="168"/>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="170"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="99"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="168"/>
-      <c r="B3" s="169"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="169"/>
-      <c r="G3" s="169"/>
-      <c r="H3" s="169"/>
-      <c r="I3" s="169"/>
-      <c r="J3" s="169"/>
-      <c r="K3" s="169"/>
-      <c r="L3" s="169"/>
-      <c r="M3" s="169"/>
-      <c r="N3" s="169"/>
-      <c r="O3" s="169"/>
-      <c r="P3" s="170"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="99"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="168"/>
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="170"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="99"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="168"/>
-      <c r="B5" s="169"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="169"/>
-      <c r="J5" s="169"/>
-      <c r="K5" s="169"/>
-      <c r="L5" s="169"/>
-      <c r="M5" s="169"/>
-      <c r="N5" s="169"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="170"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+      <c r="O5" s="98"/>
+      <c r="P5" s="99"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="168"/>
-      <c r="B6" s="169"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="170"/>
+      <c r="A6" s="97"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="99"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="168"/>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="170"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="98"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="99"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="168"/>
-      <c r="B8" s="169"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="169"/>
-      <c r="E8" s="169"/>
-      <c r="F8" s="169"/>
-      <c r="G8" s="169"/>
-      <c r="H8" s="169"/>
-      <c r="I8" s="169"/>
-      <c r="J8" s="169"/>
-      <c r="K8" s="169"/>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="170"/>
+      <c r="A8" s="97"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="99"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="168"/>
-      <c r="B9" s="169"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="169"/>
-      <c r="E9" s="169"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="169"/>
-      <c r="H9" s="169"/>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="169"/>
-      <c r="M9" s="169"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="170"/>
+      <c r="A9" s="97"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="99"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="168"/>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="169"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170"/>
+      <c r="A10" s="97"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="98"/>
+      <c r="N10" s="98"/>
+      <c r="O10" s="98"/>
+      <c r="P10" s="99"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A11" s="171"/>
-      <c r="B11" s="172"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="172"/>
-      <c r="G11" s="172"/>
-      <c r="H11" s="172"/>
-      <c r="I11" s="172"/>
-      <c r="J11" s="172"/>
-      <c r="K11" s="172"/>
-      <c r="L11" s="172"/>
-      <c r="M11" s="172"/>
-      <c r="N11" s="172"/>
-      <c r="O11" s="172"/>
-      <c r="P11" s="173"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="102"/>
     </row>
     <row r="12" spans="1:16" ht="30.75" thickBot="1">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="174" t="s">
+      <c r="C12" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="174"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="174" t="s">
+      <c r="G12" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="175"/>
+      <c r="H12" s="104"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="120"/>
+      <c r="D13" s="105"/>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>2.2046199999999998</v>
       </c>
-      <c r="G13" s="120" t="s">
+      <c r="G13" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="121"/>
-      <c r="J13" s="176" t="s">
+      <c r="H13" s="106"/>
+      <c r="J13" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="177"/>
-      <c r="L13" s="177"/>
-      <c r="M13" s="177"/>
-      <c r="N13" s="178"/>
+      <c r="K13" s="108"/>
+      <c r="L13" s="108"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="109"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="120"/>
+      <c r="D14" s="105"/>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
         <v>29.573499999999999</v>
       </c>
-      <c r="G14" s="120" t="s">
+      <c r="G14" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="121"/>
-      <c r="J14" s="148" t="s">
+      <c r="H14" s="106"/>
+      <c r="J14" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="149"/>
-      <c r="L14" s="148" t="s">
+      <c r="K14" s="111"/>
+      <c r="L14" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="120"/>
-      <c r="N14" s="121"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="106"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="120" t="s">
+      <c r="C15" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="120"/>
+      <c r="D15" s="105"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3">
         <v>28.349523125000001</v>
       </c>
-      <c r="G15" s="120" t="s">
+      <c r="G15" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="121"/>
-      <c r="J15" s="150" t="s">
+      <c r="H15" s="106"/>
+      <c r="J15" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="151"/>
-      <c r="L15" s="152" t="s">
+      <c r="K15" s="113"/>
+      <c r="L15" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="153"/>
-      <c r="N15" s="154"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="116"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="120" t="s">
+      <c r="C16" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="105"/>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2">
         <v>1000</v>
       </c>
-      <c r="G16" s="120" t="s">
+      <c r="G16" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="121"/>
-      <c r="J16" s="157" t="s">
+      <c r="H16" s="106"/>
+      <c r="J16" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="158"/>
-      <c r="L16" s="152" t="s">
+      <c r="K16" s="120"/>
+      <c r="L16" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="153"/>
-      <c r="N16" s="154"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="116"/>
     </row>
     <row r="17" spans="1:19">
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="120"/>
+      <c r="D17" s="105"/>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
         <v>1000</v>
       </c>
-      <c r="G17" s="120" t="s">
+      <c r="G17" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="121"/>
-      <c r="J17" s="159" t="s">
+      <c r="H17" s="106"/>
+      <c r="J17" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="160"/>
-      <c r="L17" s="152" t="s">
+      <c r="K17" s="122"/>
+      <c r="L17" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="153"/>
-      <c r="N17" s="154"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="116"/>
     </row>
     <row r="18" spans="1:19" ht="15.75" thickBot="1">
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="120"/>
+      <c r="D18" s="105"/>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>1000</v>
       </c>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="121"/>
-      <c r="J18" s="161" t="s">
+      <c r="H18" s="106"/>
+      <c r="J18" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="162"/>
-      <c r="L18" s="161" t="s">
+      <c r="K18" s="124"/>
+      <c r="L18" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="163"/>
-      <c r="N18" s="164"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="126"/>
     </row>
     <row r="19" spans="1:19">
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="105"/>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="3">
         <v>33.814022600000001</v>
       </c>
-      <c r="G19" s="120" t="s">
+      <c r="G19" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="121"/>
+      <c r="H19" s="106"/>
     </row>
     <row r="20" spans="1:19" ht="21.75" thickBot="1">
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="120"/>
+      <c r="D20" s="105"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="3">
         <v>0.26417205235800001</v>
       </c>
-      <c r="G20" s="120" t="s">
+      <c r="G20" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="121"/>
-      <c r="J20" s="131" t="s">
+      <c r="H20" s="106"/>
+      <c r="J20" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="K20" s="131"/>
-      <c r="L20" s="132" t="s">
+      <c r="K20" s="134"/>
+      <c r="L20" s="135" t="s">
         <v>130</v>
       </c>
-      <c r="M20" s="133"/>
-      <c r="N20" s="133"/>
+      <c r="M20" s="136"/>
+      <c r="N20" s="136"/>
     </row>
     <row r="21" spans="1:19">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="120"/>
+      <c r="D21" s="105"/>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="3">
         <v>4.9289199999999997</v>
       </c>
-      <c r="G21" s="120" t="s">
+      <c r="G21" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="121"/>
+      <c r="H21" s="106"/>
       <c r="M21" s="89">
         <v>15</v>
       </c>
-      <c r="N21" s="126" t="s">
+      <c r="N21" s="129" t="s">
         <v>39</v>
       </c>
-      <c r="O21" s="126"/>
-      <c r="P21" s="126"/>
-      <c r="Q21" s="126"/>
-      <c r="R21" s="127"/>
+      <c r="O21" s="129"/>
+      <c r="P21" s="129"/>
+      <c r="Q21" s="129"/>
+      <c r="R21" s="130"/>
     </row>
     <row r="22" spans="1:19" ht="15.6" customHeight="1">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="120"/>
+      <c r="D22" s="105"/>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>3.28084</v>
       </c>
-      <c r="G22" s="120" t="s">
+      <c r="G22" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="121"/>
+      <c r="H22" s="106"/>
       <c r="M22" s="91">
         <v>15</v>
       </c>
-      <c r="N22" s="122" t="s">
+      <c r="N22" s="151" t="s">
         <v>42</v>
       </c>
-      <c r="O22" s="122"/>
-      <c r="P22" s="122"/>
-      <c r="Q22" s="122"/>
-      <c r="R22" s="123"/>
+      <c r="O22" s="151"/>
+      <c r="P22" s="151"/>
+      <c r="Q22" s="151"/>
+      <c r="R22" s="152"/>
     </row>
     <row r="23" spans="1:19" ht="15.6" customHeight="1" thickBot="1">
       <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="155" t="s">
+      <c r="C23" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="155"/>
+      <c r="D23" s="117"/>
       <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="5">
         <v>24</v>
       </c>
-      <c r="G23" s="155" t="s">
+      <c r="G23" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="156"/>
+      <c r="H23" s="118"/>
       <c r="M23" s="92">
         <v>16</v>
       </c>
-      <c r="N23" s="124" t="s">
+      <c r="N23" s="127" t="s">
         <v>44</v>
       </c>
-      <c r="O23" s="124"/>
-      <c r="P23" s="124"/>
-      <c r="Q23" s="124"/>
-      <c r="R23" s="125"/>
+      <c r="O23" s="127"/>
+      <c r="P23" s="127"/>
+      <c r="Q23" s="127"/>
+      <c r="R23" s="128"/>
     </row>
     <row r="24" spans="1:19" ht="15.6" customHeight="1" thickBot="1">
-      <c r="A24" s="134" t="s">
+      <c r="A24" s="137" t="s">
         <v>131</v>
       </c>
-      <c r="B24" s="135"/>
-      <c r="C24" s="135"/>
-      <c r="D24" s="135"/>
-      <c r="E24" s="135"/>
-      <c r="F24" s="135"/>
-      <c r="G24" s="135"/>
-      <c r="H24" s="135"/>
-      <c r="I24" s="135"/>
-      <c r="J24" s="135"/>
-      <c r="K24" s="136"/>
+      <c r="B24" s="138"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="138"/>
+      <c r="F24" s="138"/>
+      <c r="G24" s="138"/>
+      <c r="H24" s="138"/>
+      <c r="I24" s="138"/>
+      <c r="J24" s="138"/>
+      <c r="K24" s="139"/>
       <c r="M24" s="90">
         <v>16</v>
       </c>
-      <c r="N24" s="146" t="s">
+      <c r="N24" s="149" t="s">
         <v>132</v>
       </c>
-      <c r="O24" s="146"/>
-      <c r="P24" s="146"/>
-      <c r="Q24" s="146"/>
-      <c r="R24" s="147"/>
+      <c r="O24" s="149"/>
+      <c r="P24" s="149"/>
+      <c r="Q24" s="149"/>
+      <c r="R24" s="150"/>
       <c r="S24" s="93"/>
     </row>
     <row r="25" spans="1:19" ht="15.75" hidden="1" thickBot="1">
-      <c r="A25" s="137"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="138"/>
-      <c r="F25" s="138"/>
-      <c r="G25" s="138"/>
-      <c r="H25" s="138"/>
-      <c r="I25" s="138"/>
-      <c r="J25" s="138"/>
-      <c r="K25" s="139"/>
+      <c r="A25" s="140"/>
+      <c r="B25" s="141"/>
+      <c r="C25" s="141"/>
+      <c r="D25" s="141"/>
+      <c r="E25" s="141"/>
+      <c r="F25" s="141"/>
+      <c r="G25" s="141"/>
+      <c r="H25" s="141"/>
+      <c r="I25" s="141"/>
+      <c r="J25" s="141"/>
+      <c r="K25" s="142"/>
       <c r="M25" s="82">
         <v>16</v>
       </c>
-      <c r="N25" s="128" t="s">
+      <c r="N25" s="131" t="s">
         <v>45</v>
       </c>
-      <c r="O25" s="129"/>
-      <c r="P25" s="129"/>
-      <c r="Q25" s="129"/>
-      <c r="R25" s="130"/>
+      <c r="O25" s="132"/>
+      <c r="P25" s="132"/>
+      <c r="Q25" s="132"/>
+      <c r="R25" s="133"/>
     </row>
     <row r="26" spans="1:19" hidden="1">
-      <c r="A26" s="137"/>
-      <c r="B26" s="138"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="138"/>
-      <c r="F26" s="138"/>
-      <c r="G26" s="138"/>
-      <c r="H26" s="138"/>
-      <c r="I26" s="138"/>
-      <c r="J26" s="138"/>
-      <c r="K26" s="139"/>
+      <c r="A26" s="140"/>
+      <c r="B26" s="141"/>
+      <c r="C26" s="141"/>
+      <c r="D26" s="141"/>
+      <c r="E26" s="141"/>
+      <c r="F26" s="141"/>
+      <c r="G26" s="141"/>
+      <c r="H26" s="141"/>
+      <c r="I26" s="141"/>
+      <c r="J26" s="141"/>
+      <c r="K26" s="142"/>
     </row>
     <row r="27" spans="1:19" hidden="1">
-      <c r="A27" s="137"/>
-      <c r="B27" s="138"/>
-      <c r="C27" s="138"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="138"/>
-      <c r="F27" s="138"/>
-      <c r="G27" s="138"/>
-      <c r="H27" s="138"/>
-      <c r="I27" s="138"/>
-      <c r="J27" s="138"/>
-      <c r="K27" s="139"/>
+      <c r="A27" s="140"/>
+      <c r="B27" s="141"/>
+      <c r="C27" s="141"/>
+      <c r="D27" s="141"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
+      <c r="G27" s="141"/>
+      <c r="H27" s="141"/>
+      <c r="I27" s="141"/>
+      <c r="J27" s="141"/>
+      <c r="K27" s="142"/>
     </row>
     <row r="28" spans="1:19" hidden="1">
-      <c r="A28" s="137"/>
-      <c r="B28" s="138"/>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="138"/>
-      <c r="F28" s="138"/>
-      <c r="G28" s="138"/>
-      <c r="H28" s="138"/>
-      <c r="I28" s="138"/>
-      <c r="J28" s="138"/>
-      <c r="K28" s="139"/>
+      <c r="A28" s="140"/>
+      <c r="B28" s="141"/>
+      <c r="C28" s="141"/>
+      <c r="D28" s="141"/>
+      <c r="E28" s="141"/>
+      <c r="F28" s="141"/>
+      <c r="G28" s="141"/>
+      <c r="H28" s="141"/>
+      <c r="I28" s="141"/>
+      <c r="J28" s="141"/>
+      <c r="K28" s="142"/>
     </row>
     <row r="29" spans="1:19" hidden="1">
-      <c r="A29" s="137"/>
-      <c r="B29" s="138"/>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="138"/>
-      <c r="F29" s="138"/>
-      <c r="G29" s="138"/>
-      <c r="H29" s="138"/>
-      <c r="I29" s="138"/>
-      <c r="J29" s="138"/>
-      <c r="K29" s="139"/>
+      <c r="A29" s="140"/>
+      <c r="B29" s="141"/>
+      <c r="C29" s="141"/>
+      <c r="D29" s="141"/>
+      <c r="E29" s="141"/>
+      <c r="F29" s="141"/>
+      <c r="G29" s="141"/>
+      <c r="H29" s="141"/>
+      <c r="I29" s="141"/>
+      <c r="J29" s="141"/>
+      <c r="K29" s="142"/>
     </row>
     <row r="30" spans="1:19" hidden="1">
-      <c r="A30" s="137"/>
-      <c r="B30" s="138"/>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="138"/>
-      <c r="G30" s="138"/>
-      <c r="H30" s="138"/>
-      <c r="I30" s="138"/>
-      <c r="J30" s="138"/>
-      <c r="K30" s="139"/>
+      <c r="A30" s="140"/>
+      <c r="B30" s="141"/>
+      <c r="C30" s="141"/>
+      <c r="D30" s="141"/>
+      <c r="E30" s="141"/>
+      <c r="F30" s="141"/>
+      <c r="G30" s="141"/>
+      <c r="H30" s="141"/>
+      <c r="I30" s="141"/>
+      <c r="J30" s="141"/>
+      <c r="K30" s="142"/>
     </row>
     <row r="31" spans="1:19" ht="116.25" customHeight="1" thickBot="1">
-      <c r="A31" s="140"/>
-      <c r="B31" s="141"/>
-      <c r="C31" s="141"/>
-      <c r="D31" s="141"/>
-      <c r="E31" s="141"/>
-      <c r="F31" s="141"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="141"/>
-      <c r="I31" s="141"/>
-      <c r="J31" s="141"/>
-      <c r="K31" s="142"/>
-      <c r="M31" s="143" t="s">
+      <c r="A31" s="143"/>
+      <c r="B31" s="144"/>
+      <c r="C31" s="144"/>
+      <c r="D31" s="144"/>
+      <c r="E31" s="144"/>
+      <c r="F31" s="144"/>
+      <c r="G31" s="144"/>
+      <c r="H31" s="144"/>
+      <c r="I31" s="144"/>
+      <c r="J31" s="144"/>
+      <c r="K31" s="145"/>
+      <c r="M31" s="146" t="s">
         <v>133</v>
       </c>
-      <c r="N31" s="144"/>
-      <c r="O31" s="144"/>
-      <c r="P31" s="144"/>
-      <c r="Q31" s="144"/>
-      <c r="R31" s="145"/>
+      <c r="N31" s="147"/>
+      <c r="O31" s="147"/>
+      <c r="P31" s="147"/>
+      <c r="Q31" s="147"/>
+      <c r="R31" s="148"/>
     </row>
     <row r="32" spans="1:19" ht="17.100000000000001" customHeight="1" thickBot="1">
       <c r="A32" s="11"/>
@@ -3476,19 +3490,19 @@
       <c r="C33" s="83"/>
       <c r="D33" s="83"/>
       <c r="E33" s="83"/>
-      <c r="F33" s="103" t="s">
+      <c r="F33" s="153" t="s">
         <v>134</v>
       </c>
-      <c r="G33" s="104"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="104"/>
-      <c r="J33" s="104"/>
-      <c r="K33" s="104"/>
-      <c r="L33" s="104"/>
-      <c r="M33" s="104"/>
-      <c r="N33" s="104"/>
-      <c r="O33" s="104"/>
-      <c r="P33" s="105"/>
+      <c r="G33" s="154"/>
+      <c r="H33" s="154"/>
+      <c r="I33" s="154"/>
+      <c r="J33" s="154"/>
+      <c r="K33" s="154"/>
+      <c r="L33" s="154"/>
+      <c r="M33" s="154"/>
+      <c r="N33" s="154"/>
+      <c r="O33" s="154"/>
+      <c r="P33" s="155"/>
     </row>
     <row r="34" spans="1:17" ht="30.75" thickBot="1">
       <c r="B34" s="88"/>
@@ -3537,10 +3551,10 @@
       <c r="Q34" s="77"/>
     </row>
     <row r="35" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A35" s="117" t="s">
+      <c r="A35" s="167" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="119"/>
+      <c r="B35" s="169"/>
       <c r="C35" s="62">
         <v>25</v>
       </c>
@@ -3567,9 +3581,9 @@
       <c r="J35" s="64" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="116"/>
-      <c r="L35" s="116"/>
-      <c r="M35" s="116"/>
+      <c r="K35" s="166"/>
+      <c r="L35" s="166"/>
+      <c r="M35" s="166"/>
       <c r="N35" s="64" t="s">
         <v>10</v>
       </c>
@@ -3583,10 +3597,10 @@
       <c r="Q35" s="77"/>
     </row>
     <row r="36" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A36" s="117" t="s">
+      <c r="A36" s="167" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="118"/>
+      <c r="B36" s="168"/>
       <c r="C36" s="62">
         <v>2.5</v>
       </c>
@@ -3603,9 +3617,9 @@
       </c>
       <c r="I36" s="61"/>
       <c r="J36" s="65"/>
-      <c r="K36" s="116"/>
-      <c r="L36" s="116"/>
-      <c r="M36" s="116"/>
+      <c r="K36" s="166"/>
+      <c r="L36" s="166"/>
+      <c r="M36" s="166"/>
       <c r="N36" s="64" t="s">
         <v>10</v>
       </c>
@@ -3614,10 +3628,10 @@
       <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A37" s="114" t="s">
+      <c r="A37" s="164" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="115"/>
+      <c r="B37" s="165"/>
       <c r="C37" s="62">
         <v>5</v>
       </c>
@@ -3647,28 +3661,28 @@
       <c r="Q37" s="75"/>
     </row>
     <row r="38" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A38" s="108" t="s">
+      <c r="A38" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="109"/>
-      <c r="C38" s="110"/>
-      <c r="D38" s="110"/>
-      <c r="E38" s="110"/>
-      <c r="F38" s="110"/>
-      <c r="G38" s="110"/>
-      <c r="H38" s="110"/>
-      <c r="I38" s="110"/>
-      <c r="J38" s="110"/>
-      <c r="K38" s="110"/>
-      <c r="L38" s="110"/>
-      <c r="M38" s="110"/>
-      <c r="N38" s="110"/>
-      <c r="O38" s="110"/>
-      <c r="P38" s="111"/>
+      <c r="B38" s="159"/>
+      <c r="C38" s="160"/>
+      <c r="D38" s="160"/>
+      <c r="E38" s="160"/>
+      <c r="F38" s="160"/>
+      <c r="G38" s="160"/>
+      <c r="H38" s="160"/>
+      <c r="I38" s="160"/>
+      <c r="J38" s="160"/>
+      <c r="K38" s="160"/>
+      <c r="L38" s="160"/>
+      <c r="M38" s="160"/>
+      <c r="N38" s="160"/>
+      <c r="O38" s="160"/>
+      <c r="P38" s="161"/>
     </row>
     <row r="39" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A39" s="112"/>
-      <c r="B39" s="113"/>
+      <c r="A39" s="162"/>
+      <c r="B39" s="163"/>
       <c r="C39" s="18" t="s">
         <v>47</v>
       </c>
@@ -3713,10 +3727,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A40" s="117" t="s">
+      <c r="A40" s="167" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="118"/>
+      <c r="B40" s="168"/>
       <c r="C40" s="62" t="str">
         <f>IF(L$20="Your Name!", "Enter Name in L20",ROUND(50*Random!D21,1)+1)</f>
         <v>Enter Name in L20</v>
@@ -3734,9 +3748,9 @@
       </c>
       <c r="I40" s="61"/>
       <c r="J40" s="65"/>
-      <c r="K40" s="116"/>
-      <c r="L40" s="116"/>
-      <c r="M40" s="116"/>
+      <c r="K40" s="166"/>
+      <c r="L40" s="166"/>
+      <c r="M40" s="166"/>
       <c r="N40" s="64" t="s">
         <v>10</v>
       </c>
@@ -3744,10 +3758,10 @@
       <c r="P40" s="66"/>
     </row>
     <row r="41" spans="1:17" ht="57.95" customHeight="1" thickBot="1">
-      <c r="A41" s="106" t="s">
+      <c r="A41" s="156" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="107"/>
+      <c r="B41" s="157"/>
       <c r="C41" s="62" t="str">
         <f>IF(L$20="Your Name!", "Enter Name in L20",ROUND(50*Random!D22,1)+1)</f>
         <v>Enter Name in L20</v>
@@ -3779,18 +3793,34 @@
   </sheetData>
   <sheetProtection algorithmName="SHA-512" hashValue="xYqynVFXRMtypzOki6E0FV5yKOx/aoNLP8FgcPBcwCZsd4S5Oy7xfUbX4GJVBEIXYivvt9V29puYFCTvDAmUog==" saltValue="5Rp3rBS2Sr8XjSzk2FSxgA==" spinCount="100000" sheet="1" objects="1" scenarios="1" formatCells="0" formatColumns="0" formatRows="0"/>
   <mergeCells count="56">
-    <mergeCell ref="A1:P11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="F33:P33"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="N22:R22"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="N23:R23"/>
+    <mergeCell ref="N21:R21"/>
+    <mergeCell ref="N25:R25"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="A24:K31"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="M31:R31"/>
+    <mergeCell ref="N24:R24"/>
     <mergeCell ref="J14:K14"/>
     <mergeCell ref="L14:N14"/>
     <mergeCell ref="J15:K15"/>
@@ -3807,34 +3837,18 @@
     <mergeCell ref="G20:H20"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="G21:H21"/>
-    <mergeCell ref="N23:R23"/>
-    <mergeCell ref="N21:R21"/>
-    <mergeCell ref="N25:R25"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="A24:K31"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="G22:H22"/>
-    <mergeCell ref="M31:R31"/>
-    <mergeCell ref="N24:R24"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="N22:R22"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
-    <mergeCell ref="F33:P33"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="K40:M40"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="A1:P11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:N13"/>
   </mergeCells>
   <conditionalFormatting sqref="F36:F37 I36:I37 O36:O37 L37 F40:F41 I40:I41 O40:O41 L41">
     <cfRule type="expression" dxfId="2" priority="2">
@@ -3870,6 +3884,172 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E99E579A-3FB7-49E7-9A28-0D2F1BE1915D}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.140625" style="71"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" s="71" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="209">
+        <v>1</v>
+      </c>
+      <c r="D1" t="str">
+        <f>Conversions!L20</f>
+        <v>Your Name!</v>
+      </c>
+      <c r="F1" s="210" t="str">
+        <f ca="1">IF(M1="ACTIVE", "✓ Tracking Active", "⚠️ ERROR: Enable Iterative Calculations (File &gt; Options &gt; Formulas)")</f>
+        <v>✓ Tracking Active</v>
+      </c>
+      <c r="G1" s="210"/>
+      <c r="H1" s="210"/>
+      <c r="I1" s="210"/>
+      <c r="J1" s="210"/>
+      <c r="K1" s="210"/>
+      <c r="L1" s="210"/>
+      <c r="M1" s="71" t="str">
+        <f ca="1">IF(M1="ACTIVE", "ACTIVE", "ACTIVE")</f>
+        <v>ACTIVE</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="71" t="str">
+        <f t="shared" ref="A2:A19" ca="1" si="0">IF(D$1&lt;&gt;A3,A3,A2)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="71" t="str">
+        <f t="shared" ca="1" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="71" t="str">
+        <f ca="1">IF(D$1&lt;&gt;A21,A21,A20)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="71" t="str">
+        <f ca="1">IF(C1="","",IF(D$1&lt;&gt;A21,D$1,A21))</f>
+        <v>Your Name!</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="06PtncHppB8CMS55kuqFwN3KFi3ByMwHh7l7odPSMuBJyOHsRuEU+XJpENHZVHL3XQYCtjKs/L+51EjcZUSiyw==" saltValue="KcWbuioN1+Rg16E/kwJeWA==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <mergeCells count="1">
+    <mergeCell ref="F1:L1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AEF4E6C-368D-4542-83C3-C132C34F33C8}">
   <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5905,7 +6085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B5CACFC-F0F6-481D-A675-4F2F82948D64}">
   <dimension ref="A1:Q41"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -5917,590 +6097,590 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="15" customHeight="1">
-      <c r="A1" s="165" t="s">
+      <c r="A1" s="94" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="166"/>
-      <c r="C1" s="166"/>
-      <c r="D1" s="166"/>
-      <c r="E1" s="166"/>
-      <c r="F1" s="166"/>
-      <c r="G1" s="166"/>
-      <c r="H1" s="166"/>
-      <c r="I1" s="166"/>
-      <c r="J1" s="166"/>
-      <c r="K1" s="166"/>
-      <c r="L1" s="166"/>
-      <c r="M1" s="166"/>
-      <c r="N1" s="166"/>
-      <c r="O1" s="166"/>
-      <c r="P1" s="167"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
+      <c r="H1" s="95"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="95"/>
+      <c r="L1" s="95"/>
+      <c r="M1" s="95"/>
+      <c r="N1" s="95"/>
+      <c r="O1" s="95"/>
+      <c r="P1" s="96"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="168"/>
-      <c r="B2" s="169"/>
-      <c r="C2" s="169"/>
-      <c r="D2" s="169"/>
-      <c r="E2" s="169"/>
-      <c r="F2" s="169"/>
-      <c r="G2" s="169"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="169"/>
-      <c r="K2" s="169"/>
-      <c r="L2" s="169"/>
-      <c r="M2" s="169"/>
-      <c r="N2" s="169"/>
-      <c r="O2" s="169"/>
-      <c r="P2" s="170"/>
+      <c r="A2" s="97"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="98"/>
+      <c r="I2" s="98"/>
+      <c r="J2" s="98"/>
+      <c r="K2" s="98"/>
+      <c r="L2" s="98"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="98"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="99"/>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" s="168"/>
-      <c r="B3" s="169"/>
-      <c r="C3" s="169"/>
-      <c r="D3" s="169"/>
-      <c r="E3" s="169"/>
-      <c r="F3" s="169"/>
-      <c r="G3" s="169"/>
-      <c r="H3" s="169"/>
-      <c r="I3" s="169"/>
-      <c r="J3" s="169"/>
-      <c r="K3" s="169"/>
-      <c r="L3" s="169"/>
-      <c r="M3" s="169"/>
-      <c r="N3" s="169"/>
-      <c r="O3" s="169"/>
-      <c r="P3" s="170"/>
+      <c r="A3" s="97"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="98"/>
+      <c r="G3" s="98"/>
+      <c r="H3" s="98"/>
+      <c r="I3" s="98"/>
+      <c r="J3" s="98"/>
+      <c r="K3" s="98"/>
+      <c r="L3" s="98"/>
+      <c r="M3" s="98"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="98"/>
+      <c r="P3" s="99"/>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" s="168"/>
-      <c r="B4" s="169"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="170"/>
+      <c r="A4" s="97"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
+      <c r="F4" s="98"/>
+      <c r="G4" s="98"/>
+      <c r="H4" s="98"/>
+      <c r="I4" s="98"/>
+      <c r="J4" s="98"/>
+      <c r="K4" s="98"/>
+      <c r="L4" s="98"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="99"/>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" s="168"/>
-      <c r="B5" s="169"/>
-      <c r="C5" s="169"/>
-      <c r="D5" s="169"/>
-      <c r="E5" s="169"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="169"/>
-      <c r="H5" s="169"/>
-      <c r="I5" s="169"/>
-      <c r="J5" s="169"/>
-      <c r="K5" s="169"/>
-      <c r="L5" s="169"/>
-      <c r="M5" s="169"/>
-      <c r="N5" s="169"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="170"/>
+      <c r="A5" s="97"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="98"/>
+      <c r="D5" s="98"/>
+      <c r="E5" s="98"/>
+      <c r="F5" s="98"/>
+      <c r="G5" s="98"/>
+      <c r="H5" s="98"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
+      <c r="K5" s="98"/>
+      <c r="L5" s="98"/>
+      <c r="M5" s="98"/>
+      <c r="N5" s="98"/>
+      <c r="O5" s="98"/>
+      <c r="P5" s="99"/>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" s="168"/>
-      <c r="B6" s="169"/>
-      <c r="C6" s="169"/>
-      <c r="D6" s="169"/>
-      <c r="E6" s="169"/>
-      <c r="F6" s="169"/>
-      <c r="G6" s="169"/>
-      <c r="H6" s="169"/>
-      <c r="I6" s="169"/>
-      <c r="J6" s="169"/>
-      <c r="K6" s="169"/>
-      <c r="L6" s="169"/>
-      <c r="M6" s="169"/>
-      <c r="N6" s="169"/>
-      <c r="O6" s="169"/>
-      <c r="P6" s="170"/>
+      <c r="A6" s="97"/>
+      <c r="B6" s="98"/>
+      <c r="C6" s="98"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="98"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="98"/>
+      <c r="H6" s="98"/>
+      <c r="I6" s="98"/>
+      <c r="J6" s="98"/>
+      <c r="K6" s="98"/>
+      <c r="L6" s="98"/>
+      <c r="M6" s="98"/>
+      <c r="N6" s="98"/>
+      <c r="O6" s="98"/>
+      <c r="P6" s="99"/>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" s="168"/>
-      <c r="B7" s="169"/>
-      <c r="C7" s="169"/>
-      <c r="D7" s="169"/>
-      <c r="E7" s="169"/>
-      <c r="F7" s="169"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="169"/>
-      <c r="I7" s="169"/>
-      <c r="J7" s="169"/>
-      <c r="K7" s="169"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="169"/>
-      <c r="N7" s="169"/>
-      <c r="O7" s="169"/>
-      <c r="P7" s="170"/>
+      <c r="A7" s="97"/>
+      <c r="B7" s="98"/>
+      <c r="C7" s="98"/>
+      <c r="D7" s="98"/>
+      <c r="E7" s="98"/>
+      <c r="F7" s="98"/>
+      <c r="G7" s="98"/>
+      <c r="H7" s="98"/>
+      <c r="I7" s="98"/>
+      <c r="J7" s="98"/>
+      <c r="K7" s="98"/>
+      <c r="L7" s="98"/>
+      <c r="M7" s="98"/>
+      <c r="N7" s="98"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="99"/>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" s="168"/>
-      <c r="B8" s="169"/>
-      <c r="C8" s="169"/>
-      <c r="D8" s="169"/>
-      <c r="E8" s="169"/>
-      <c r="F8" s="169"/>
-      <c r="G8" s="169"/>
-      <c r="H8" s="169"/>
-      <c r="I8" s="169"/>
-      <c r="J8" s="169"/>
-      <c r="K8" s="169"/>
-      <c r="L8" s="169"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="170"/>
+      <c r="A8" s="97"/>
+      <c r="B8" s="98"/>
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98"/>
+      <c r="K8" s="98"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
+      <c r="N8" s="98"/>
+      <c r="O8" s="98"/>
+      <c r="P8" s="99"/>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" s="168"/>
-      <c r="B9" s="169"/>
-      <c r="C9" s="169"/>
-      <c r="D9" s="169"/>
-      <c r="E9" s="169"/>
-      <c r="F9" s="169"/>
-      <c r="G9" s="169"/>
-      <c r="H9" s="169"/>
-      <c r="I9" s="169"/>
-      <c r="J9" s="169"/>
-      <c r="K9" s="169"/>
-      <c r="L9" s="169"/>
-      <c r="M9" s="169"/>
-      <c r="N9" s="169"/>
-      <c r="O9" s="169"/>
-      <c r="P9" s="170"/>
+      <c r="A9" s="97"/>
+      <c r="B9" s="98"/>
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="98"/>
+      <c r="F9" s="98"/>
+      <c r="G9" s="98"/>
+      <c r="H9" s="98"/>
+      <c r="I9" s="98"/>
+      <c r="J9" s="98"/>
+      <c r="K9" s="98"/>
+      <c r="L9" s="98"/>
+      <c r="M9" s="98"/>
+      <c r="N9" s="98"/>
+      <c r="O9" s="98"/>
+      <c r="P9" s="99"/>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" s="168"/>
-      <c r="B10" s="169"/>
-      <c r="C10" s="169"/>
-      <c r="D10" s="169"/>
-      <c r="E10" s="169"/>
-      <c r="F10" s="169"/>
-      <c r="G10" s="169"/>
-      <c r="H10" s="169"/>
-      <c r="I10" s="169"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="170"/>
+      <c r="A10" s="97"/>
+      <c r="B10" s="98"/>
+      <c r="C10" s="98"/>
+      <c r="D10" s="98"/>
+      <c r="E10" s="98"/>
+      <c r="F10" s="98"/>
+      <c r="G10" s="98"/>
+      <c r="H10" s="98"/>
+      <c r="I10" s="98"/>
+      <c r="J10" s="98"/>
+      <c r="K10" s="98"/>
+      <c r="L10" s="98"/>
+      <c r="M10" s="98"/>
+      <c r="N10" s="98"/>
+      <c r="O10" s="98"/>
+      <c r="P10" s="99"/>
     </row>
     <row r="11" spans="1:16" ht="15.75" thickBot="1">
-      <c r="A11" s="171"/>
-      <c r="B11" s="172"/>
-      <c r="C11" s="172"/>
-      <c r="D11" s="172"/>
-      <c r="E11" s="172"/>
-      <c r="F11" s="172"/>
-      <c r="G11" s="172"/>
-      <c r="H11" s="172"/>
-      <c r="I11" s="172"/>
-      <c r="J11" s="172"/>
-      <c r="K11" s="172"/>
-      <c r="L11" s="172"/>
-      <c r="M11" s="172"/>
-      <c r="N11" s="172"/>
-      <c r="O11" s="172"/>
-      <c r="P11" s="173"/>
+      <c r="A11" s="100"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="101"/>
+      <c r="I11" s="101"/>
+      <c r="J11" s="101"/>
+      <c r="K11" s="101"/>
+      <c r="L11" s="101"/>
+      <c r="M11" s="101"/>
+      <c r="N11" s="101"/>
+      <c r="O11" s="101"/>
+      <c r="P11" s="102"/>
     </row>
     <row r="12" spans="1:16" ht="30.75" thickBot="1">
       <c r="B12" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="174" t="s">
+      <c r="C12" s="103" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="174"/>
+      <c r="D12" s="103"/>
       <c r="E12" s="7" t="s">
         <v>10</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="174" t="s">
+      <c r="G12" s="103" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="175"/>
+      <c r="H12" s="104"/>
     </row>
     <row r="13" spans="1:16">
       <c r="B13" s="1">
         <v>1</v>
       </c>
-      <c r="C13" s="120" t="s">
+      <c r="C13" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="120"/>
+      <c r="D13" s="105"/>
       <c r="E13" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="2">
         <v>2.2046199999999998</v>
       </c>
-      <c r="G13" s="120" t="s">
+      <c r="G13" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="121"/>
-      <c r="J13" s="176" t="s">
+      <c r="H13" s="106"/>
+      <c r="J13" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="K13" s="177"/>
-      <c r="L13" s="177"/>
-      <c r="M13" s="177"/>
-      <c r="N13" s="178"/>
+      <c r="K13" s="108"/>
+      <c r="L13" s="108"/>
+      <c r="M13" s="108"/>
+      <c r="N13" s="109"/>
     </row>
     <row r="14" spans="1:16">
       <c r="B14" s="1">
         <v>1</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="120"/>
+      <c r="D14" s="105"/>
       <c r="E14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="2">
         <v>29.573499999999999</v>
       </c>
-      <c r="G14" s="120" t="s">
+      <c r="G14" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="H14" s="121"/>
-      <c r="J14" s="148" t="s">
+      <c r="H14" s="106"/>
+      <c r="J14" s="110" t="s">
         <v>18</v>
       </c>
-      <c r="K14" s="149"/>
-      <c r="L14" s="148" t="s">
+      <c r="K14" s="111"/>
+      <c r="L14" s="110" t="s">
         <v>19</v>
       </c>
-      <c r="M14" s="120"/>
-      <c r="N14" s="121"/>
+      <c r="M14" s="105"/>
+      <c r="N14" s="106"/>
     </row>
     <row r="15" spans="1:16">
       <c r="B15" s="1">
         <v>1</v>
       </c>
-      <c r="C15" s="120" t="s">
+      <c r="C15" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="120"/>
+      <c r="D15" s="105"/>
       <c r="E15" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="3">
         <v>28.349523125000001</v>
       </c>
-      <c r="G15" s="120" t="s">
+      <c r="G15" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="H15" s="121"/>
-      <c r="J15" s="150" t="s">
+      <c r="H15" s="106"/>
+      <c r="J15" s="112" t="s">
         <v>22</v>
       </c>
-      <c r="K15" s="151"/>
-      <c r="L15" s="152" t="s">
+      <c r="K15" s="113"/>
+      <c r="L15" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="M15" s="153"/>
-      <c r="N15" s="154"/>
+      <c r="M15" s="115"/>
+      <c r="N15" s="116"/>
     </row>
     <row r="16" spans="1:16">
       <c r="B16" s="1">
         <v>1</v>
       </c>
-      <c r="C16" s="120" t="s">
+      <c r="C16" s="105" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="105"/>
       <c r="E16" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="2">
         <v>1000</v>
       </c>
-      <c r="G16" s="120" t="s">
+      <c r="G16" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="H16" s="121"/>
-      <c r="J16" s="157" t="s">
+      <c r="H16" s="106"/>
+      <c r="J16" s="119" t="s">
         <v>24</v>
       </c>
-      <c r="K16" s="158"/>
-      <c r="L16" s="152" t="s">
+      <c r="K16" s="120"/>
+      <c r="L16" s="114" t="s">
         <v>25</v>
       </c>
-      <c r="M16" s="153"/>
-      <c r="N16" s="154"/>
+      <c r="M16" s="115"/>
+      <c r="N16" s="116"/>
     </row>
     <row r="17" spans="1:14">
       <c r="B17" s="1">
         <v>1</v>
       </c>
-      <c r="C17" s="120" t="s">
+      <c r="C17" s="105" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="120"/>
+      <c r="D17" s="105"/>
       <c r="E17" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="2">
         <v>1000</v>
       </c>
-      <c r="G17" s="120" t="s">
+      <c r="G17" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="H17" s="121"/>
-      <c r="J17" s="159" t="s">
+      <c r="H17" s="106"/>
+      <c r="J17" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="K17" s="160"/>
-      <c r="L17" s="152" t="s">
+      <c r="K17" s="122"/>
+      <c r="L17" s="114" t="s">
         <v>28</v>
       </c>
-      <c r="M17" s="153"/>
-      <c r="N17" s="154"/>
+      <c r="M17" s="115"/>
+      <c r="N17" s="116"/>
     </row>
     <row r="18" spans="1:14" ht="15.75" thickBot="1">
       <c r="B18" s="1">
         <v>1</v>
       </c>
-      <c r="C18" s="120" t="s">
+      <c r="C18" s="105" t="s">
         <v>26</v>
       </c>
-      <c r="D18" s="120"/>
+      <c r="D18" s="105"/>
       <c r="E18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="2">
         <v>1000</v>
       </c>
-      <c r="G18" s="120" t="s">
+      <c r="G18" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="121"/>
-      <c r="J18" s="161" t="s">
+      <c r="H18" s="106"/>
+      <c r="J18" s="123" t="s">
         <v>30</v>
       </c>
-      <c r="K18" s="162"/>
-      <c r="L18" s="161" t="s">
+      <c r="K18" s="124"/>
+      <c r="L18" s="123" t="s">
         <v>31</v>
       </c>
-      <c r="M18" s="163"/>
-      <c r="N18" s="164"/>
+      <c r="M18" s="125"/>
+      <c r="N18" s="126"/>
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="1">
         <v>1</v>
       </c>
-      <c r="C19" s="120" t="s">
+      <c r="C19" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="105"/>
       <c r="E19" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F19" s="3">
         <v>33.814022600000001</v>
       </c>
-      <c r="G19" s="120" t="s">
+      <c r="G19" s="105" t="s">
         <v>33</v>
       </c>
-      <c r="H19" s="121"/>
+      <c r="H19" s="106"/>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="120" t="s">
+      <c r="C20" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="D20" s="120"/>
+      <c r="D20" s="105"/>
       <c r="E20" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="3">
         <v>0.26417205235800001</v>
       </c>
-      <c r="G20" s="120" t="s">
+      <c r="G20" s="105" t="s">
         <v>34</v>
       </c>
-      <c r="H20" s="121"/>
+      <c r="H20" s="106"/>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="1">
         <v>1</v>
       </c>
-      <c r="C21" s="120" t="s">
+      <c r="C21" s="105" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="120"/>
+      <c r="D21" s="105"/>
       <c r="E21" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="3">
         <v>4.9289199999999997</v>
       </c>
-      <c r="G21" s="120" t="s">
+      <c r="G21" s="105" t="s">
         <v>17</v>
       </c>
-      <c r="H21" s="121"/>
+      <c r="H21" s="106"/>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="1">
         <v>1</v>
       </c>
-      <c r="C22" s="120" t="s">
+      <c r="C22" s="105" t="s">
         <v>37</v>
       </c>
-      <c r="D22" s="120"/>
+      <c r="D22" s="105"/>
       <c r="E22" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F22" s="3">
         <v>3.28084</v>
       </c>
-      <c r="G22" s="120" t="s">
+      <c r="G22" s="105" t="s">
         <v>38</v>
       </c>
-      <c r="H22" s="121"/>
+      <c r="H22" s="106"/>
     </row>
     <row r="23" spans="1:14" ht="15.75" thickBot="1">
       <c r="B23" s="4">
         <v>1</v>
       </c>
-      <c r="C23" s="155" t="s">
+      <c r="C23" s="117" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="155"/>
+      <c r="D23" s="117"/>
       <c r="E23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="F23" s="5">
         <v>24</v>
       </c>
-      <c r="G23" s="155" t="s">
+      <c r="G23" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="H23" s="156"/>
+      <c r="H23" s="118"/>
     </row>
     <row r="24" spans="1:14" ht="15" customHeight="1">
-      <c r="A24" s="165" t="s">
+      <c r="A24" s="94" t="s">
         <v>43</v>
       </c>
-      <c r="B24" s="166"/>
-      <c r="C24" s="166"/>
-      <c r="D24" s="166"/>
-      <c r="E24" s="166"/>
-      <c r="F24" s="166"/>
-      <c r="G24" s="166"/>
-      <c r="H24" s="166"/>
-      <c r="I24" s="166"/>
-      <c r="J24" s="166"/>
-      <c r="K24" s="167"/>
+      <c r="B24" s="95"/>
+      <c r="C24" s="95"/>
+      <c r="D24" s="95"/>
+      <c r="E24" s="95"/>
+      <c r="F24" s="95"/>
+      <c r="G24" s="95"/>
+      <c r="H24" s="95"/>
+      <c r="I24" s="95"/>
+      <c r="J24" s="95"/>
+      <c r="K24" s="96"/>
     </row>
     <row r="25" spans="1:14">
-      <c r="A25" s="168"/>
-      <c r="B25" s="169"/>
-      <c r="C25" s="169"/>
-      <c r="D25" s="169"/>
-      <c r="E25" s="169"/>
-      <c r="F25" s="169"/>
-      <c r="G25" s="169"/>
-      <c r="H25" s="169"/>
-      <c r="I25" s="169"/>
-      <c r="J25" s="169"/>
-      <c r="K25" s="170"/>
+      <c r="A25" s="97"/>
+      <c r="B25" s="98"/>
+      <c r="C25" s="98"/>
+      <c r="D25" s="98"/>
+      <c r="E25" s="98"/>
+      <c r="F25" s="98"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="98"/>
+      <c r="I25" s="98"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="99"/>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="168"/>
-      <c r="B26" s="169"/>
-      <c r="C26" s="169"/>
-      <c r="D26" s="169"/>
-      <c r="E26" s="169"/>
-      <c r="F26" s="169"/>
-      <c r="G26" s="169"/>
-      <c r="H26" s="169"/>
-      <c r="I26" s="169"/>
-      <c r="J26" s="169"/>
-      <c r="K26" s="170"/>
+      <c r="A26" s="97"/>
+      <c r="B26" s="98"/>
+      <c r="C26" s="98"/>
+      <c r="D26" s="98"/>
+      <c r="E26" s="98"/>
+      <c r="F26" s="98"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="98"/>
+      <c r="I26" s="98"/>
+      <c r="J26" s="98"/>
+      <c r="K26" s="99"/>
     </row>
     <row r="27" spans="1:14">
-      <c r="A27" s="168"/>
-      <c r="B27" s="169"/>
-      <c r="C27" s="169"/>
-      <c r="D27" s="169"/>
-      <c r="E27" s="169"/>
-      <c r="F27" s="169"/>
-      <c r="G27" s="169"/>
-      <c r="H27" s="169"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="170"/>
+      <c r="A27" s="97"/>
+      <c r="B27" s="98"/>
+      <c r="C27" s="98"/>
+      <c r="D27" s="98"/>
+      <c r="E27" s="98"/>
+      <c r="F27" s="98"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="98"/>
+      <c r="I27" s="98"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="99"/>
     </row>
     <row r="28" spans="1:14">
-      <c r="A28" s="168"/>
-      <c r="B28" s="169"/>
-      <c r="C28" s="169"/>
-      <c r="D28" s="169"/>
-      <c r="E28" s="169"/>
-      <c r="F28" s="169"/>
-      <c r="G28" s="169"/>
-      <c r="H28" s="169"/>
-      <c r="I28" s="169"/>
-      <c r="J28" s="169"/>
-      <c r="K28" s="170"/>
+      <c r="A28" s="97"/>
+      <c r="B28" s="98"/>
+      <c r="C28" s="98"/>
+      <c r="D28" s="98"/>
+      <c r="E28" s="98"/>
+      <c r="F28" s="98"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="98"/>
+      <c r="I28" s="98"/>
+      <c r="J28" s="98"/>
+      <c r="K28" s="99"/>
     </row>
     <row r="29" spans="1:14">
-      <c r="A29" s="168"/>
-      <c r="B29" s="169"/>
-      <c r="C29" s="169"/>
-      <c r="D29" s="169"/>
-      <c r="E29" s="169"/>
-      <c r="F29" s="169"/>
-      <c r="G29" s="169"/>
-      <c r="H29" s="169"/>
-      <c r="I29" s="169"/>
-      <c r="J29" s="169"/>
-      <c r="K29" s="170"/>
+      <c r="A29" s="97"/>
+      <c r="B29" s="98"/>
+      <c r="C29" s="98"/>
+      <c r="D29" s="98"/>
+      <c r="E29" s="98"/>
+      <c r="F29" s="98"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="98"/>
+      <c r="I29" s="98"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="99"/>
     </row>
     <row r="30" spans="1:14">
-      <c r="A30" s="168"/>
-      <c r="B30" s="169"/>
-      <c r="C30" s="169"/>
-      <c r="D30" s="169"/>
-      <c r="E30" s="169"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="169"/>
-      <c r="J30" s="169"/>
-      <c r="K30" s="170"/>
+      <c r="A30" s="97"/>
+      <c r="B30" s="98"/>
+      <c r="C30" s="98"/>
+      <c r="D30" s="98"/>
+      <c r="E30" s="98"/>
+      <c r="F30" s="98"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="98"/>
+      <c r="I30" s="98"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="99"/>
     </row>
     <row r="31" spans="1:14" ht="15.75" thickBot="1">
-      <c r="A31" s="171"/>
-      <c r="B31" s="172"/>
-      <c r="C31" s="172"/>
-      <c r="D31" s="172"/>
-      <c r="E31" s="172"/>
-      <c r="F31" s="172"/>
-      <c r="G31" s="172"/>
-      <c r="H31" s="172"/>
-      <c r="I31" s="172"/>
-      <c r="J31" s="172"/>
-      <c r="K31" s="173"/>
+      <c r="A31" s="100"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="101"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="102"/>
     </row>
     <row r="32" spans="1:14" ht="15.75" thickBot="1">
       <c r="A32" s="11"/>
@@ -6516,28 +6696,28 @@
       <c r="K32" s="10"/>
     </row>
     <row r="33" spans="1:17" ht="16.5" customHeight="1" thickBot="1">
-      <c r="A33" s="197" t="s">
+      <c r="A33" s="182" t="s">
         <v>46</v>
       </c>
-      <c r="B33" s="198"/>
-      <c r="C33" s="198"/>
-      <c r="D33" s="198"/>
-      <c r="E33" s="198"/>
-      <c r="F33" s="198"/>
-      <c r="G33" s="198"/>
-      <c r="H33" s="198"/>
-      <c r="I33" s="198"/>
-      <c r="J33" s="198"/>
-      <c r="K33" s="198"/>
-      <c r="L33" s="198"/>
-      <c r="M33" s="198"/>
-      <c r="N33" s="198"/>
-      <c r="O33" s="198"/>
-      <c r="P33" s="199"/>
+      <c r="B33" s="183"/>
+      <c r="C33" s="183"/>
+      <c r="D33" s="183"/>
+      <c r="E33" s="183"/>
+      <c r="F33" s="183"/>
+      <c r="G33" s="183"/>
+      <c r="H33" s="183"/>
+      <c r="I33" s="183"/>
+      <c r="J33" s="183"/>
+      <c r="K33" s="183"/>
+      <c r="L33" s="183"/>
+      <c r="M33" s="183"/>
+      <c r="N33" s="183"/>
+      <c r="O33" s="183"/>
+      <c r="P33" s="184"/>
     </row>
     <row r="34" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A34" s="190"/>
-      <c r="B34" s="191"/>
+      <c r="A34" s="185"/>
+      <c r="B34" s="186"/>
       <c r="C34" s="9" t="s">
         <v>47</v>
       </c>
@@ -6585,10 +6765,10 @@
       </c>
     </row>
     <row r="35" spans="1:17" ht="45.75" customHeight="1" thickBot="1">
-      <c r="A35" s="194" t="s">
+      <c r="A35" s="179" t="s">
         <v>57</v>
       </c>
-      <c r="B35" s="195"/>
+      <c r="B35" s="180"/>
       <c r="C35" s="14">
         <v>25</v>
       </c>
@@ -6615,9 +6795,9 @@
       <c r="J35" s="35" t="s">
         <v>60</v>
       </c>
-      <c r="K35" s="196"/>
-      <c r="L35" s="196"/>
-      <c r="M35" s="196"/>
+      <c r="K35" s="181"/>
+      <c r="L35" s="181"/>
+      <c r="M35" s="181"/>
       <c r="N35" s="35" t="s">
         <v>10</v>
       </c>
@@ -6633,10 +6813,10 @@
       </c>
     </row>
     <row r="36" spans="1:17" ht="33.950000000000003" customHeight="1" thickBot="1">
-      <c r="A36" s="181" t="s">
+      <c r="A36" s="189" t="s">
         <v>63</v>
       </c>
-      <c r="B36" s="182"/>
+      <c r="B36" s="190"/>
       <c r="C36" s="14">
         <v>2.5</v>
       </c>
@@ -6663,9 +6843,9 @@
       <c r="J36" s="46" t="s">
         <v>122</v>
       </c>
-      <c r="K36" s="183"/>
-      <c r="L36" s="116"/>
-      <c r="M36" s="184"/>
+      <c r="K36" s="191"/>
+      <c r="L36" s="166"/>
+      <c r="M36" s="192"/>
       <c r="N36" s="35" t="s">
         <v>10</v>
       </c>
@@ -6679,10 +6859,10 @@
       <c r="Q36" s="12"/>
     </row>
     <row r="37" spans="1:17" ht="48.6" customHeight="1" thickBot="1">
-      <c r="A37" s="185" t="s">
+      <c r="A37" s="193" t="s">
         <v>65</v>
       </c>
-      <c r="B37" s="186"/>
+      <c r="B37" s="194"/>
       <c r="C37" s="14">
         <v>5</v>
       </c>
@@ -6732,28 +6912,28 @@
       <c r="Q37" s="13"/>
     </row>
     <row r="38" spans="1:17" ht="19.5" thickBot="1">
-      <c r="A38" s="187" t="s">
+      <c r="A38" s="195" t="s">
         <v>67</v>
       </c>
-      <c r="B38" s="188"/>
-      <c r="C38" s="188"/>
-      <c r="D38" s="188"/>
-      <c r="E38" s="188"/>
-      <c r="F38" s="188"/>
-      <c r="G38" s="188"/>
-      <c r="H38" s="188"/>
-      <c r="I38" s="188"/>
-      <c r="J38" s="188"/>
-      <c r="K38" s="188"/>
-      <c r="L38" s="188"/>
-      <c r="M38" s="188"/>
-      <c r="N38" s="188"/>
-      <c r="O38" s="188"/>
-      <c r="P38" s="189"/>
+      <c r="B38" s="196"/>
+      <c r="C38" s="196"/>
+      <c r="D38" s="196"/>
+      <c r="E38" s="196"/>
+      <c r="F38" s="196"/>
+      <c r="G38" s="196"/>
+      <c r="H38" s="196"/>
+      <c r="I38" s="196"/>
+      <c r="J38" s="196"/>
+      <c r="K38" s="196"/>
+      <c r="L38" s="196"/>
+      <c r="M38" s="196"/>
+      <c r="N38" s="196"/>
+      <c r="O38" s="196"/>
+      <c r="P38" s="197"/>
     </row>
     <row r="39" spans="1:17" ht="30.75" thickBot="1">
-      <c r="A39" s="190"/>
-      <c r="B39" s="191"/>
+      <c r="A39" s="185"/>
+      <c r="B39" s="186"/>
       <c r="C39" s="18" t="s">
         <v>47</v>
       </c>
@@ -6798,10 +6978,10 @@
       </c>
     </row>
     <row r="40" spans="1:17" ht="48.95" customHeight="1" thickBot="1">
-      <c r="A40" s="181" t="s">
+      <c r="A40" s="189" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="182"/>
+      <c r="B40" s="190"/>
       <c r="C40" s="19" t="str">
         <f>Conversions!C40</f>
         <v>Enter Name in L20</v>
@@ -6829,9 +7009,9 @@
       <c r="J40" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="K40" s="192"/>
-      <c r="L40" s="192"/>
-      <c r="M40" s="193"/>
+      <c r="K40" s="198"/>
+      <c r="L40" s="198"/>
+      <c r="M40" s="199"/>
       <c r="N40" s="26" t="s">
         <v>10</v>
       </c>
@@ -6844,10 +7024,10 @@
       </c>
     </row>
     <row r="41" spans="1:17" ht="48.95" customHeight="1" thickBot="1">
-      <c r="A41" s="179" t="s">
+      <c r="A41" s="187" t="s">
         <v>69</v>
       </c>
-      <c r="B41" s="180"/>
+      <c r="B41" s="188"/>
       <c r="C41" s="20" t="str">
         <f>Conversions!C41</f>
         <v>Enter Name in L20</v>
@@ -6898,34 +7078,14 @@
     </row>
   </sheetData>
   <mergeCells count="49">
-    <mergeCell ref="A1:P11"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="J13:N13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="J14:K14"/>
-    <mergeCell ref="L14:N14"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="K36:M36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A38:P38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="K40:M40"/>
     <mergeCell ref="A35:B35"/>
     <mergeCell ref="K35:M35"/>
     <mergeCell ref="C20:D20"/>
@@ -6939,14 +7099,34 @@
     <mergeCell ref="A24:K31"/>
     <mergeCell ref="A33:P33"/>
     <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="K36:M36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:P38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="K40:M40"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="G19:H19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="J14:K14"/>
+    <mergeCell ref="L14:N14"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="A1:P11"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="J13:N13"/>
   </mergeCells>
   <conditionalFormatting sqref="F40 I40">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6959,7 +7139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094BBAA7-7892-4AED-B159-88642EDC59F0}">
   <dimension ref="B1:F5"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -7016,6 +7196,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002C289946819CFF499E91D197BC975371" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="674b7a4e239a9748c7aaa97e309327a4">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cca9fd2d-ef84-45c9-8063-8f4bd4c29606" xmlns:ns3="18557d39-01b8-4d71-9479-3fad465290ae" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="600253478e594d1349e02792803dc53a" ns2:_="" ns3:_="">
     <xsd:import namespace="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
@@ -7232,16 +7422,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="cca9fd2d-ef84-45c9-8063-8f4bd4c29606">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF3B6B4C-EC0E-4746-BC50-2C3213BAC25B}">
   <ds:schemaRefs>
@@ -7251,6 +7431,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D29BAF0-14B6-4E1B-BA72-51F7164DDA8E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E75299CF-40C1-4653-959B-0AE66E133E77}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7267,14 +7457,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D29BAF0-14B6-4E1B-BA72-51F7164DDA8E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="cca9fd2d-ef84-45c9-8063-8f4bd4c29606"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>